--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3D9C078-0120-44A4-A4DA-261C6F599853}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6CD88D2-17A5-4C6C-8E30-82310FFEC7E1}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-1260" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="221">
   <si>
     <t>ID</t>
   </si>
@@ -479,29 +479,245 @@
   </si>
   <si>
     <t>lagoa-bonita</t>
+  </si>
+  <si>
+    <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t>RK</t>
+  </si>
+  <si>
+    <t>Vander Silva;</t>
+  </si>
+  <si>
+    <t>Victoria Virgens;</t>
+  </si>
+  <si>
+    <t>Reynaldo Santos;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R MICHELÂNGELO, Num.: 191 Comple.: , Bairro: JARDIM MITSUTANI / </t>
+  </si>
+  <si>
+    <t>SERGIO@PLASTICOSINDEP.COM.BR;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 91648-5026 / </t>
+  </si>
+  <si>
+    <t>GABRIEL PALADINO RAUNAIMER; BRUNO PALADINO RAUNAIMER;</t>
+  </si>
+  <si>
+    <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Ourinhos, Num.: 205 Comple.: , Bairro: Parque Industrial das Oliveiras / </t>
+  </si>
+  <si>
+    <t>sergio@plasticosindep.com.br;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 91648-5026 / </t>
+  </si>
+  <si>
+    <t>SERGIO TADEU RAUNAIMER;ELAINE APARECIDA MOLINARI ZAMORA;</t>
+  </si>
+  <si>
+    <t>SANTOS &amp; DIAN MATERIAIS PARA CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t>SD MATERIAIS</t>
+  </si>
+  <si>
+    <t>Bruno Contieri;</t>
+  </si>
+  <si>
+    <t>Daniela Silva;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVENIDA PROFESSOR PEDRO CLARISMUNDO FORNARI, Num.: 1490 Comple.: , Bairro: ENGORDADOURO / </t>
+  </si>
+  <si>
+    <t>financeiro@sdmaterialdeconstrucao.com.br;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 4582-5121 / </t>
+  </si>
+  <si>
+    <t>WILSON APARECIDO DIAN;</t>
+  </si>
+  <si>
+    <t>COMERCIO VAREJISTA DE MERCADORIAS 3M LTDA (MATRIZ)</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO 3M</t>
+  </si>
+  <si>
+    <t>Daniel Oliveira;</t>
+  </si>
+  <si>
+    <t>Clara Maria;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Alberto Borges Soveral, Num.: 09 Comple.: COM FUNDOS PARA A RUA PIETRO DA MILANO 55, Bairro: Parque Independência / </t>
+  </si>
+  <si>
+    <t>MARCOSMARTINS@SUPERMERCADO3M.COM.BR;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 5832-2100 Ramal 229 - Cel: 11 95911-9371 / </t>
+  </si>
+  <si>
+    <t>AA&amp;amp;MARTINS PARTICIPACOES LTDA;ADRIANO AUGUSTO MARTINS;E&amp;amp;G MARTINS PARTICIPACOES LTDA;EDUARDO DE JESUS MARTINS; B&amp;amp;SOLAR PARTICIPACOES LTDA;MARCOS MARQUES MARTINS;</t>
+  </si>
+  <si>
+    <t>COMERCIO VAREJISTA DE MERCADORIAS 3M LTDA (FILIAL 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Feitiço da Vila, Num.: 36 Comple.: , Bairro: Chácara Santa Maria / </t>
+  </si>
+  <si>
+    <t>ADRIANO AUGUSTO MARTINS;EDUARDO DE JESUS MARTINS;AA&amp;amp;MARTINS PARTICIPACOES LTDA;MARCOS MARQUES MARTINS; B&amp;amp;SOLAR PARTICIPACOES LTDA;E&amp;amp;G MARTINS PARTICIPACOES LTDA;</t>
+  </si>
+  <si>
+    <t>MARQUES &amp; MARTINS ADMINISTRADORA DE BENS PROPRIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avenida Giovanni Gronchi, Num.: 6195 Comple.: SALA 813, Bairro: Vila Andrade / </t>
+  </si>
+  <si>
+    <t>marcosmartins@supermercado3m.com.br;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 5832-2100 / </t>
+  </si>
+  <si>
+    <t>Holding</t>
+  </si>
+  <si>
+    <t>MARCOS MARQUES MARTINS;</t>
+  </si>
+  <si>
+    <t>FRUTAS DA TERRA HORTIFRUTI LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Alberto Borges Soveral, Num.: 23 Comple.: , Bairro: Parque Independência / </t>
+  </si>
+  <si>
+    <t>contabil@supermercados3m.com.br;</t>
+  </si>
+  <si>
+    <t>E&amp;G MARTINS PARTICIPAÇÕES LTDA</t>
+  </si>
+  <si>
+    <t>Karine Gusmão;</t>
+  </si>
+  <si>
+    <t>Isabelli Afonso;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avenida Giovanni Gronchi, Num.: 6195 Comple.: Sala 813, Bairro: Vila Andrade / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 4741-0807 / </t>
+  </si>
+  <si>
+    <t>EDUARDO DE JESUS MARTINS;</t>
+  </si>
+  <si>
+    <t>E&amp;G MARTINS ADMINISTRACAO DE BENS PROPRIOS LTDA</t>
+  </si>
+  <si>
+    <t>B&amp;SOLAR PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t>B&amp;SOLAR ADMINISTRACAO DE BENS PROPRIOS LTDA</t>
+  </si>
+  <si>
+    <t>AA&amp;MARTINS ADMINISTRACAO DE BENS PROPRIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avenida Giovanni Gronchi, Num.: 6195 Comple.: Sala 13, Bairro: Vila Andrade / </t>
+  </si>
+  <si>
+    <t>ADRIANO AUGUSTO MARTINS;</t>
+  </si>
+  <si>
+    <t>AA&amp;MARTINS PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t>ALDENIR VENANCIO DE OLIVEIRA LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO CRISTO REI</t>
+  </si>
+  <si>
+    <t>Ricardo Ferreira;</t>
+  </si>
+  <si>
+    <t>GOMES SERVIÇOS - LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA JERÔNIMO VILELA, Num.: 271 Comple.: QUADRA 27 LOTE 13, Bairro: VILA SOFIA / </t>
+  </si>
+  <si>
+    <t>venanciopardal@hotmail.com;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64 996444975 / </t>
+  </si>
+  <si>
+    <t>ALDENIR VENANCIO DE OLIVEIRA;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA MINAS GERAIS, Num.: 698 Comple.: QUADRA 48 - LOTE 10A - SALA 01, Bairro: VILA SANTA MARIA / </t>
+  </si>
+  <si>
+    <t>alineferasoadm@hotmial.com;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(64) 99647-7060 / </t>
+  </si>
+  <si>
+    <t>ARMANDO GOMES DE ASSIS;</t>
+  </si>
+  <si>
+    <t>E&amp;amp;G MARTINS PARTICIPACOES LTDA;EDUARDO DE JESUS MARTINS; AA&amp;amp;MARTINS PARTICIPACOES LTDA;ADRIANO AUGUSTO MARTINS; B&amp;amp;SOLAR PARTICIPACOES LTDA;MARCOS MARQUES MARTINS;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -518,27 +734,16 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="1">
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -553,20 +758,16 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T19">
-  <autoFilter ref="A1:T19" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T34">
+  <autoFilter ref="A1:T34" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T19">
-    <sortCondition ref="T1:T19"/>
+    <sortCondition ref="D1:D19"/>
   </sortState>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" totalsRowFunction="average"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="RazaoSocial" totalsRowFunction="average"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ContratoMG" totalsRowFunction="average" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ContratoMG" totalsRowFunction="average" dataDxfId="0"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Grupo" totalsRowFunction="average"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Gerente" totalsRowFunction="average"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Secretaria" totalsRowFunction="average"/>
@@ -578,14 +779,14 @@
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Segmento" totalsRowFunction="average"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Socio" totalsRowFunction="average"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Implantação CTB"/>
-    <tableColumn id="7" xr3:uid="{0AFAB906-C921-447F-AE27-262AE6DF88B4}" name="Implantação CTB - Realizada" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{0AFAB906-C921-447F-AE27-262AE6DF88B4}" name="Implantação CTB - Realizada"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Implantação EF"/>
-    <tableColumn id="8" xr3:uid="{5B2D038A-745A-4A1C-8CCD-0A7265A0AA57}" name="Implantação EF - Realizada" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{5B2D038A-745A-4A1C-8CCD-0A7265A0AA57}" name="Implantação EF - Realizada"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Implantação DP"/>
     <tableColumn id="9" xr3:uid="{4EC4A72A-B6C2-47C3-A66B-DB898C2CE30E}" name="Implantação DP - Realizada"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="GrupoID"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -906,12 +1107,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="72.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
@@ -938,7 +1139,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1160,6 +1361,9 @@
       <c r="Q4" t="s">
         <v>149</v>
       </c>
+      <c r="R4">
+        <v>46253</v>
+      </c>
       <c r="S4" t="s">
         <v>150</v>
       </c>
@@ -1208,10 +1412,13 @@
         <v>46232</v>
       </c>
       <c r="Q5" t="s">
-        <v>150</v>
+        <v>149</v>
+      </c>
+      <c r="R5">
+        <v>46253</v>
       </c>
       <c r="S5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T5" t="s">
         <v>46</v>
@@ -1269,6 +1476,9 @@
       <c r="Q6" t="s">
         <v>150</v>
       </c>
+      <c r="R6">
+        <v>46246</v>
+      </c>
       <c r="S6" t="s">
         <v>150</v>
       </c>
@@ -1328,6 +1538,9 @@
       <c r="Q7" t="s">
         <v>150</v>
       </c>
+      <c r="R7">
+        <v>46246</v>
+      </c>
       <c r="S7" t="s">
         <v>150</v>
       </c>
@@ -1381,6 +1594,9 @@
       <c r="Q8" t="s">
         <v>150</v>
       </c>
+      <c r="R8">
+        <v>46253</v>
+      </c>
       <c r="S8" t="s">
         <v>150</v>
       </c>
@@ -1490,7 +1706,7 @@
       <c r="S10" t="s">
         <v>149</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="T10" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1538,12 +1754,12 @@
         <v>150</v>
       </c>
       <c r="Q11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S11" t="s">
         <v>150</v>
       </c>
-      <c r="T11" s="3" t="s">
+      <c r="T11" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1594,15 +1810,18 @@
         <v>150</v>
       </c>
       <c r="P12">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="Q12" t="s">
         <v>150</v>
       </c>
+      <c r="R12">
+        <v>46245</v>
+      </c>
       <c r="S12" t="s">
         <v>150</v>
       </c>
-      <c r="T12" s="2" t="s">
+      <c r="T12" t="s">
         <v>151</v>
       </c>
     </row>
@@ -1836,7 +2055,10 @@
         <v>46233</v>
       </c>
       <c r="Q16" t="s">
-        <v>150</v>
+        <v>149</v>
+      </c>
+      <c r="R16">
+        <v>46251</v>
       </c>
       <c r="S16" t="s">
         <v>150</v>
@@ -1886,16 +2108,16 @@
         <v>130</v>
       </c>
       <c r="N17">
-        <v>46233</v>
+        <v>46241</v>
       </c>
       <c r="O17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P17">
-        <v>46233</v>
+        <v>46241</v>
       </c>
       <c r="Q17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S17" t="s">
         <v>149</v>
@@ -1964,7 +2186,7 @@
       <c r="B19" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19">
         <v>46266</v>
       </c>
       <c r="D19" t="s">
@@ -2003,11 +2225,764 @@
       <c r="Q19" t="s">
         <v>150</v>
       </c>
+      <c r="R19">
+        <v>46248</v>
+      </c>
       <c r="S19" t="s">
         <v>150</v>
       </c>
       <c r="T19" t="s">
         <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>7005</v>
+      </c>
+      <c r="B20" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20">
+        <v>46266</v>
+      </c>
+      <c r="D20" t="s">
+        <v>154</v>
+      </c>
+      <c r="E20" t="s">
+        <v>155</v>
+      </c>
+      <c r="F20" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" t="s">
+        <v>157</v>
+      </c>
+      <c r="H20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" t="s">
+        <v>158</v>
+      </c>
+      <c r="J20" t="s">
+        <v>159</v>
+      </c>
+      <c r="K20" t="s">
+        <v>160</v>
+      </c>
+      <c r="L20" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" t="s">
+        <v>161</v>
+      </c>
+      <c r="O20" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>150</v>
+      </c>
+      <c r="S20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>7006</v>
+      </c>
+      <c r="B21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C21">
+        <v>46266</v>
+      </c>
+      <c r="D21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" t="s">
+        <v>155</v>
+      </c>
+      <c r="F21" t="s">
+        <v>156</v>
+      </c>
+      <c r="G21" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" t="s">
+        <v>163</v>
+      </c>
+      <c r="J21" t="s">
+        <v>164</v>
+      </c>
+      <c r="K21" t="s">
+        <v>165</v>
+      </c>
+      <c r="L21" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" t="s">
+        <v>166</v>
+      </c>
+      <c r="O21" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>150</v>
+      </c>
+      <c r="S21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>7007</v>
+      </c>
+      <c r="B22" t="s">
+        <v>167</v>
+      </c>
+      <c r="C22">
+        <v>46266</v>
+      </c>
+      <c r="D22" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" t="s">
+        <v>169</v>
+      </c>
+      <c r="F22" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" t="s">
+        <v>157</v>
+      </c>
+      <c r="H22" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" t="s">
+        <v>171</v>
+      </c>
+      <c r="J22" t="s">
+        <v>172</v>
+      </c>
+      <c r="K22" t="s">
+        <v>173</v>
+      </c>
+      <c r="L22" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" t="s">
+        <v>174</v>
+      </c>
+      <c r="O22" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>150</v>
+      </c>
+      <c r="S22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>7012</v>
+      </c>
+      <c r="B23" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23">
+        <v>46235</v>
+      </c>
+      <c r="D23" t="s">
+        <v>176</v>
+      </c>
+      <c r="E23" t="s">
+        <v>177</v>
+      </c>
+      <c r="F23" t="s">
+        <v>178</v>
+      </c>
+      <c r="G23" t="s">
+        <v>157</v>
+      </c>
+      <c r="H23" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" t="s">
+        <v>179</v>
+      </c>
+      <c r="J23" t="s">
+        <v>180</v>
+      </c>
+      <c r="K23" t="s">
+        <v>181</v>
+      </c>
+      <c r="L23" t="s">
+        <v>55</v>
+      </c>
+      <c r="M23" t="s">
+        <v>182</v>
+      </c>
+      <c r="O23" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>150</v>
+      </c>
+      <c r="S23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>7013</v>
+      </c>
+      <c r="B24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C24">
+        <v>46235</v>
+      </c>
+      <c r="D24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E24" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24" t="s">
+        <v>178</v>
+      </c>
+      <c r="G24" t="s">
+        <v>157</v>
+      </c>
+      <c r="H24" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" t="s">
+        <v>184</v>
+      </c>
+      <c r="J24" t="s">
+        <v>180</v>
+      </c>
+      <c r="K24" t="s">
+        <v>181</v>
+      </c>
+      <c r="L24" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" t="s">
+        <v>185</v>
+      </c>
+      <c r="O24" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>150</v>
+      </c>
+      <c r="S24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>7014</v>
+      </c>
+      <c r="B25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25">
+        <v>46235</v>
+      </c>
+      <c r="D25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25" t="s">
+        <v>177</v>
+      </c>
+      <c r="F25" t="s">
+        <v>178</v>
+      </c>
+      <c r="G25" t="s">
+        <v>157</v>
+      </c>
+      <c r="H25" t="s">
+        <v>87</v>
+      </c>
+      <c r="I25" t="s">
+        <v>187</v>
+      </c>
+      <c r="J25" t="s">
+        <v>188</v>
+      </c>
+      <c r="K25" t="s">
+        <v>189</v>
+      </c>
+      <c r="L25" t="s">
+        <v>190</v>
+      </c>
+      <c r="M25" t="s">
+        <v>191</v>
+      </c>
+      <c r="O25" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>150</v>
+      </c>
+      <c r="S25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>7015</v>
+      </c>
+      <c r="B26" t="s">
+        <v>192</v>
+      </c>
+      <c r="C26">
+        <v>46235</v>
+      </c>
+      <c r="D26" t="s">
+        <v>176</v>
+      </c>
+      <c r="E26" t="s">
+        <v>177</v>
+      </c>
+      <c r="F26" t="s">
+        <v>178</v>
+      </c>
+      <c r="G26" t="s">
+        <v>157</v>
+      </c>
+      <c r="H26" t="s">
+        <v>87</v>
+      </c>
+      <c r="I26" t="s">
+        <v>193</v>
+      </c>
+      <c r="J26" t="s">
+        <v>194</v>
+      </c>
+      <c r="K26" t="s">
+        <v>181</v>
+      </c>
+      <c r="L26" t="s">
+        <v>55</v>
+      </c>
+      <c r="M26" t="s">
+        <v>220</v>
+      </c>
+      <c r="O26" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>150</v>
+      </c>
+      <c r="S26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>7016</v>
+      </c>
+      <c r="B27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27">
+        <v>46235</v>
+      </c>
+      <c r="D27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F27" t="s">
+        <v>197</v>
+      </c>
+      <c r="G27" t="s">
+        <v>157</v>
+      </c>
+      <c r="H27" t="s">
+        <v>87</v>
+      </c>
+      <c r="I27" t="s">
+        <v>198</v>
+      </c>
+      <c r="J27" t="s">
+        <v>188</v>
+      </c>
+      <c r="K27" t="s">
+        <v>199</v>
+      </c>
+      <c r="L27" t="s">
+        <v>190</v>
+      </c>
+      <c r="M27" t="s">
+        <v>200</v>
+      </c>
+      <c r="O27" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>150</v>
+      </c>
+      <c r="S27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>7017</v>
+      </c>
+      <c r="B28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C28">
+        <v>46235</v>
+      </c>
+      <c r="D28" t="s">
+        <v>176</v>
+      </c>
+      <c r="E28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G28" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" t="s">
+        <v>87</v>
+      </c>
+      <c r="I28" t="s">
+        <v>187</v>
+      </c>
+      <c r="J28" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" t="s">
+        <v>181</v>
+      </c>
+      <c r="L28" t="s">
+        <v>55</v>
+      </c>
+      <c r="M28" t="s">
+        <v>200</v>
+      </c>
+      <c r="O28" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>150</v>
+      </c>
+      <c r="S28" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>7018</v>
+      </c>
+      <c r="B29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29">
+        <v>46235</v>
+      </c>
+      <c r="D29" t="s">
+        <v>176</v>
+      </c>
+      <c r="E29" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" t="s">
+        <v>197</v>
+      </c>
+      <c r="G29" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29" t="s">
+        <v>87</v>
+      </c>
+      <c r="I29" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" t="s">
+        <v>180</v>
+      </c>
+      <c r="K29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L29" t="s">
+        <v>55</v>
+      </c>
+      <c r="M29" t="s">
+        <v>191</v>
+      </c>
+      <c r="O29" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>150</v>
+      </c>
+      <c r="S29" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>7019</v>
+      </c>
+      <c r="B30" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30">
+        <v>46235</v>
+      </c>
+      <c r="D30" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30" t="s">
+        <v>178</v>
+      </c>
+      <c r="G30" t="s">
+        <v>157</v>
+      </c>
+      <c r="H30" t="s">
+        <v>87</v>
+      </c>
+      <c r="I30" t="s">
+        <v>187</v>
+      </c>
+      <c r="J30" t="s">
+        <v>194</v>
+      </c>
+      <c r="K30" t="s">
+        <v>181</v>
+      </c>
+      <c r="L30" t="s">
+        <v>55</v>
+      </c>
+      <c r="M30" t="s">
+        <v>191</v>
+      </c>
+      <c r="O30" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>150</v>
+      </c>
+      <c r="S30" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>7020</v>
+      </c>
+      <c r="B31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C31">
+        <v>46235</v>
+      </c>
+      <c r="D31" t="s">
+        <v>176</v>
+      </c>
+      <c r="E31" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31" t="s">
+        <v>157</v>
+      </c>
+      <c r="H31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I31" t="s">
+        <v>205</v>
+      </c>
+      <c r="J31" t="s">
+        <v>188</v>
+      </c>
+      <c r="K31" t="s">
+        <v>199</v>
+      </c>
+      <c r="L31" t="s">
+        <v>190</v>
+      </c>
+      <c r="M31" t="s">
+        <v>206</v>
+      </c>
+      <c r="O31" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>150</v>
+      </c>
+      <c r="S31" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>7021</v>
+      </c>
+      <c r="B32" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32">
+        <v>46235</v>
+      </c>
+      <c r="D32" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" t="s">
+        <v>196</v>
+      </c>
+      <c r="F32" t="s">
+        <v>197</v>
+      </c>
+      <c r="G32" t="s">
+        <v>157</v>
+      </c>
+      <c r="H32" t="s">
+        <v>87</v>
+      </c>
+      <c r="I32" t="s">
+        <v>198</v>
+      </c>
+      <c r="J32" t="s">
+        <v>188</v>
+      </c>
+      <c r="K32" t="s">
+        <v>199</v>
+      </c>
+      <c r="L32" t="s">
+        <v>190</v>
+      </c>
+      <c r="M32" t="s">
+        <v>206</v>
+      </c>
+      <c r="O32" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>150</v>
+      </c>
+      <c r="S32" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>6992</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="2">
+        <v>46266</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="O33" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>150</v>
+      </c>
+      <c r="S33" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>6993</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C34" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="O34" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>150</v>
+      </c>
+      <c r="S34" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6CD88D2-17A5-4C6C-8E30-82310FFEC7E1}"/>
+  <xr:revisionPtr revIDLastSave="346" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{659E3508-6A00-45D5-A7B9-691998C0B6CE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-1260" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="227">
   <si>
     <t>ID</t>
   </si>
@@ -683,13 +683,32 @@
   </si>
   <si>
     <t>E&amp;amp;G MARTINS PARTICIPACOES LTDA;EDUARDO DE JESUS MARTINS; AA&amp;amp;MARTINS PARTICIPACOES LTDA;ADRIANO AUGUSTO MARTINS; B&amp;amp;SOLAR PARTICIPACOES LTDA;MARCOS MARQUES MARTINS;</t>
+  </si>
+  <si>
+    <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRASIL DISTRIBUIDORA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA DOS JUNQUILHOS, Num.: 153 Comple.: LOTE 26 - QUADRA 08 - SALA 01, Bairro: PARQUE OESTE INDUSTRIAL /
+ </t>
+  </si>
+  <si>
+    <t>brasildistribuidoradepecas@gmail.com;</t>
+  </si>
+  <si>
+    <t>(62) 8180-4195 /</t>
+  </si>
+  <si>
+    <t>CLEY MARCOS FIDELIS;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -702,6 +721,17 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -729,16 +759,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -758,9 +795,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T34">
-  <autoFilter ref="A1:T34" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T35">
+  <autoFilter ref="A1:T35" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T19">
     <sortCondition ref="D1:D19"/>
   </sortState>
@@ -1107,29 +1148,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:T35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="72.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="115.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="120.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="43.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="64.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="192" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="27" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -1337,7 +1378,7 @@
       <c r="I4" t="s">
         <v>42</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="4" t="s">
         <v>43</v>
       </c>
       <c r="K4" t="s">
@@ -1644,11 +1685,20 @@
       <c r="M9" t="s">
         <v>75</v>
       </c>
+      <c r="N9">
+        <v>46255</v>
+      </c>
       <c r="O9" t="s">
         <v>150</v>
       </c>
+      <c r="P9">
+        <v>46255</v>
+      </c>
       <c r="Q9" t="s">
         <v>150</v>
+      </c>
+      <c r="R9">
+        <v>46191</v>
       </c>
       <c r="S9" t="s">
         <v>149</v>
@@ -1697,11 +1747,20 @@
       <c r="M10" t="s">
         <v>81</v>
       </c>
+      <c r="N10">
+        <v>46255</v>
+      </c>
       <c r="O10" t="s">
         <v>150</v>
       </c>
+      <c r="P10">
+        <v>46255</v>
+      </c>
       <c r="Q10" t="s">
         <v>150</v>
+      </c>
+      <c r="R10">
+        <v>46191</v>
       </c>
       <c r="S10" t="s">
         <v>149</v>
@@ -1835,7 +1894,7 @@
       <c r="C13">
         <v>46266</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E13" t="s">
@@ -2166,11 +2225,20 @@
       <c r="M18" t="s">
         <v>137</v>
       </c>
+      <c r="N18">
+        <v>46205</v>
+      </c>
       <c r="O18" t="s">
         <v>149</v>
       </c>
+      <c r="P18">
+        <v>46205</v>
+      </c>
       <c r="Q18" t="s">
         <v>149</v>
+      </c>
+      <c r="R18">
+        <v>46216</v>
       </c>
       <c r="S18" t="s">
         <v>149</v>
@@ -2437,7 +2505,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>7013</v>
+        <v>7012</v>
       </c>
       <c r="B24" t="s">
         <v>183</v>
@@ -2931,6 +2999,9 @@
       <c r="Q33" t="s">
         <v>150</v>
       </c>
+      <c r="R33">
+        <v>46247</v>
+      </c>
       <c r="S33" t="s">
         <v>150</v>
       </c>
@@ -2981,14 +3052,80 @@
       <c r="Q34" t="s">
         <v>150</v>
       </c>
+      <c r="R34">
+        <v>46247</v>
+      </c>
       <c r="S34" t="s">
         <v>150</v>
       </c>
     </row>
+    <row r="35" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>6945</v>
+      </c>
+      <c r="B35" t="s">
+        <v>221</v>
+      </c>
+      <c r="C35" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D35" t="s">
+        <v>222</v>
+      </c>
+      <c r="E35" t="s">
+        <v>155</v>
+      </c>
+      <c r="F35" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" t="s">
+        <v>157</v>
+      </c>
+      <c r="H35" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="K35" t="s">
+        <v>225</v>
+      </c>
+      <c r="L35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" t="s">
+        <v>226</v>
+      </c>
+      <c r="N35">
+        <v>46219</v>
+      </c>
+      <c r="O35" t="s">
+        <v>150</v>
+      </c>
+      <c r="P35">
+        <v>46219</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>150</v>
+      </c>
+      <c r="R35">
+        <v>46217</v>
+      </c>
+      <c r="S35" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J4" r:id="rId1" xr:uid="{0FBB74B0-7BDF-4CCB-902E-06F540839053}"/>
+    <hyperlink ref="J35" r:id="rId2" xr:uid="{66BBE0A7-BDDD-4208-88F5-EC986E31CB14}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="346" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{659E3508-6A00-45D5-A7B9-691998C0B6CE}"/>
+  <xr:revisionPtr revIDLastSave="357" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F4ABBC1-7B23-4103-8804-46AA31A8F007}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-1260" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" r:id="rId1"/>
@@ -1933,8 +1933,8 @@
       <c r="P13">
         <v>46259</v>
       </c>
-      <c r="Q13" t="s">
-        <v>149</v>
+      <c r="Q13" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="R13">
         <v>46245</v>
@@ -3087,7 +3087,7 @@
       <c r="I35" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="J35" s="4" t="s">
+      <c r="J35" s="1" t="s">
         <v>224</v>
       </c>
       <c r="K35" t="s">

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="357" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F4ABBC1-7B23-4103-8804-46AA31A8F007}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" r:id="rId1"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="357" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F4ABBC1-7B23-4103-8804-46AA31A8F007}"/>
+  <xr:revisionPtr revIDLastSave="391" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFDA0571-C6BB-4559-BB8F-B18A0B54658E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -64,12 +80,21 @@
     <t>Implantação CTB</t>
   </si>
   <si>
+    <t>Implantação CTB - Realizada</t>
+  </si>
+  <si>
     <t>Implantação EF</t>
   </si>
   <si>
+    <t>Implantação EF - Realizada</t>
+  </si>
+  <si>
     <t>Implantação DP</t>
   </si>
   <si>
+    <t>Implantação DP - Realizada</t>
+  </si>
+  <si>
     <t>GrupoID</t>
   </si>
   <si>
@@ -106,6 +131,9 @@
     <t>RAFAELA YUMI TUKAMOTO;</t>
   </si>
   <si>
+    <t>Não</t>
+  </si>
+  <si>
     <t>atria-cenografia</t>
   </si>
   <si>
@@ -160,6 +188,9 @@
     <t>JACINTO DE OLIVEIRA NETO;CÁRITAS NEIVA VIEIRA FRANÇA;</t>
   </si>
   <si>
+    <t>Sim</t>
+  </si>
+  <si>
     <t>film-facil</t>
   </si>
   <si>
@@ -298,6 +329,9 @@
     <t>JOEL CHERUBIM DE BARROS;</t>
   </si>
   <si>
+    <t>lagoa-bonita</t>
+  </si>
+  <si>
     <t>SUPER DIJAN COMERCIAL LTDA</t>
   </si>
   <si>
@@ -325,6 +359,9 @@
     <t>JANDUI RODRIGUES DE MIRANDA; FELIPE DIJAN SANTOS DE MIRANDA;</t>
   </si>
   <si>
+    <t>mercado-dijan</t>
+  </si>
+  <si>
     <t>F. MARQUES DE SA LTDA</t>
   </si>
   <si>
@@ -460,27 +497,6 @@
     <t>trizga</t>
   </si>
   <si>
-    <t>Implantação CTB - Realizada</t>
-  </si>
-  <si>
-    <t>Implantação EF - Realizada</t>
-  </si>
-  <si>
-    <t>Implantação DP - Realizada</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>mercado-dijan</t>
-  </si>
-  <si>
-    <t>lagoa-bonita</t>
-  </si>
-  <si>
     <t>INDEP INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
   </si>
   <si>
@@ -607,6 +623,9 @@
     <t>contabil@supermercados3m.com.br;</t>
   </si>
   <si>
+    <t>E&amp;amp;G MARTINS PARTICIPACOES LTDA;EDUARDO DE JESUS MARTINS; AA&amp;amp;MARTINS PARTICIPACOES LTDA;ADRIANO AUGUSTO MARTINS; B&amp;amp;SOLAR PARTICIPACOES LTDA;MARCOS MARQUES MARTINS;</t>
+  </si>
+  <si>
     <t>E&amp;G MARTINS PARTICIPAÇÕES LTDA</t>
   </si>
   <si>
@@ -655,21 +674,21 @@
     <t>Ricardo Ferreira;</t>
   </si>
   <si>
+    <t xml:space="preserve">RUA JERÔNIMO VILELA, Num.: 271 Comple.: QUADRA 27 LOTE 13, Bairro: VILA SOFIA / </t>
+  </si>
+  <si>
+    <t>venanciopardal@hotmail.com;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64 996444975 / </t>
+  </si>
+  <si>
+    <t>ALDENIR VENANCIO DE OLIVEIRA;</t>
+  </si>
+  <si>
     <t>GOMES SERVIÇOS - LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">RUA JERÔNIMO VILELA, Num.: 271 Comple.: QUADRA 27 LOTE 13, Bairro: VILA SOFIA / </t>
-  </si>
-  <si>
-    <t>venanciopardal@hotmail.com;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64 996444975 / </t>
-  </si>
-  <si>
-    <t>ALDENIR VENANCIO DE OLIVEIRA;</t>
-  </si>
-  <si>
     <t xml:space="preserve">RUA MINAS GERAIS, Num.: 698 Comple.: QUADRA 48 - LOTE 10A - SALA 01, Bairro: VILA SANTA MARIA / </t>
   </si>
   <si>
@@ -680,9 +699,6 @@
   </si>
   <si>
     <t>ARMANDO GOMES DE ASSIS;</t>
-  </si>
-  <si>
-    <t>E&amp;amp;G MARTINS PARTICIPACOES LTDA;EDUARDO DE JESUS MARTINS; AA&amp;amp;MARTINS PARTICIPACOES LTDA;ADRIANO AUGUSTO MARTINS; B&amp;amp;SOLAR PARTICIPACOES LTDA;MARCOS MARQUES MARTINS;</t>
   </si>
   <si>
     <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
@@ -708,7 +724,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -763,7 +779,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -773,12 +789,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
@@ -795,10 +821,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T35">
   <autoFilter ref="A1:T35" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
@@ -808,7 +830,7 @@
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" totalsRowFunction="average"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="RazaoSocial" totalsRowFunction="average"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ContratoMG" totalsRowFunction="average" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ContratoMG" totalsRowFunction="average" dataDxfId="3"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Grupo" totalsRowFunction="average"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Gerente" totalsRowFunction="average"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Secretaria" totalsRowFunction="average"/>
@@ -819,11 +841,11 @@
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Telefone" totalsRowFunction="average"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Segmento" totalsRowFunction="average"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Socio" totalsRowFunction="average"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Implantação CTB"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Implantação CTB" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{0AFAB906-C921-447F-AE27-262AE6DF88B4}" name="Implantação CTB - Realizada"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Implantação EF"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Implantação EF" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{5B2D038A-745A-4A1C-8CCD-0A7265A0AA57}" name="Implantação EF - Realizada"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Implantação DP"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Implantação DP" dataDxfId="0"/>
     <tableColumn id="9" xr3:uid="{4EC4A72A-B6C2-47C3-A66B-DB898C2CE30E}" name="Implantação DP - Realizada"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="GrupoID"/>
   </tableColumns>
@@ -1149,31 +1171,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="72.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="120.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="45.42578125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="43.28515625" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="192" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="192" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="18" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="27" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" style="7" customWidth="1"/>
     <col min="19" max="19" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.85546875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1213,1097 +1236,1097 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q1" t="s">
-        <v>147</v>
-      </c>
-      <c r="R1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>148</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2">
         <v>6989</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>46220</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S2" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3">
         <v>6812</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>46266</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3">
+        <v>41</v>
+      </c>
+      <c r="N3" s="7">
         <v>46260</v>
       </c>
       <c r="O3" t="s">
-        <v>150</v>
-      </c>
-      <c r="P3">
+        <v>31</v>
+      </c>
+      <c r="P3" s="7">
         <v>46260</v>
       </c>
       <c r="Q3" t="s">
-        <v>150</v>
-      </c>
-      <c r="R3">
+        <v>31</v>
+      </c>
+      <c r="R3" s="7">
         <v>46251</v>
       </c>
       <c r="S3" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4">
         <v>6976</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C4">
         <v>46235</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4">
+        <v>49</v>
+      </c>
+      <c r="N4" s="7">
         <v>46232</v>
       </c>
       <c r="O4" t="s">
-        <v>150</v>
-      </c>
-      <c r="P4">
+        <v>31</v>
+      </c>
+      <c r="P4" s="7">
         <v>46232</v>
       </c>
       <c r="Q4" t="s">
-        <v>149</v>
-      </c>
-      <c r="R4">
+        <v>50</v>
+      </c>
+      <c r="R4" s="7">
         <v>46253</v>
       </c>
       <c r="S4" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="A5">
         <v>6977</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>46235</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M5" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5">
+        <v>53</v>
+      </c>
+      <c r="N5" s="7">
         <v>46232</v>
       </c>
       <c r="O5" t="s">
-        <v>150</v>
-      </c>
-      <c r="P5">
+        <v>31</v>
+      </c>
+      <c r="P5" s="7">
         <v>46232</v>
       </c>
       <c r="Q5" t="s">
-        <v>149</v>
-      </c>
-      <c r="R5">
+        <v>50</v>
+      </c>
+      <c r="R5" s="7">
         <v>46253</v>
       </c>
       <c r="S5" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="A6">
         <v>6966</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>46235</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M6" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6">
+        <v>61</v>
+      </c>
+      <c r="N6" s="7">
         <v>46245</v>
       </c>
       <c r="O6" t="s">
-        <v>150</v>
-      </c>
-      <c r="P6">
+        <v>31</v>
+      </c>
+      <c r="P6" s="7">
         <v>46245</v>
       </c>
       <c r="Q6" t="s">
-        <v>150</v>
-      </c>
-      <c r="R6">
+        <v>31</v>
+      </c>
+      <c r="R6" s="7">
         <v>46246</v>
       </c>
       <c r="S6" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="A7">
         <v>6967</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>46235</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L7" t="s">
         <v>60</v>
       </c>
-      <c r="K7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L7" t="s">
-        <v>55</v>
-      </c>
       <c r="M7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" s="7">
+        <v>46245</v>
+      </c>
+      <c r="O7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" s="7">
+        <v>46245</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>31</v>
+      </c>
+      <c r="R7" s="7">
+        <v>46246</v>
+      </c>
+      <c r="S7" t="s">
+        <v>31</v>
+      </c>
+      <c r="T7" t="s">
         <v>62</v>
       </c>
-      <c r="N7">
-        <v>46245</v>
-      </c>
-      <c r="O7" t="s">
-        <v>150</v>
-      </c>
-      <c r="P7">
-        <v>46245</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>150</v>
-      </c>
-      <c r="R7">
-        <v>46246</v>
-      </c>
-      <c r="S7" t="s">
-        <v>150</v>
-      </c>
-      <c r="T7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:20">
       <c r="A8">
         <v>6978</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C8">
         <v>46266</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="O8" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q8" t="s">
-        <v>150</v>
-      </c>
-      <c r="R8">
+        <v>31</v>
+      </c>
+      <c r="R8" s="7">
         <v>46253</v>
       </c>
       <c r="S8" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="A9">
         <v>6923</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C9">
         <v>46204</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M9" t="s">
-        <v>75</v>
-      </c>
-      <c r="N9">
+        <v>80</v>
+      </c>
+      <c r="N9" s="7">
         <v>46255</v>
       </c>
       <c r="O9" t="s">
-        <v>150</v>
-      </c>
-      <c r="P9">
+        <v>31</v>
+      </c>
+      <c r="P9" s="7">
         <v>46255</v>
       </c>
       <c r="Q9" t="s">
-        <v>150</v>
-      </c>
-      <c r="R9">
+        <v>31</v>
+      </c>
+      <c r="R9" s="7">
         <v>46191</v>
       </c>
       <c r="S9" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="T9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10">
         <v>6924</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C10">
         <v>46204</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J10" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K10" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M10" t="s">
+        <v>86</v>
+      </c>
+      <c r="N10" s="7">
+        <v>46255</v>
+      </c>
+      <c r="O10" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" s="7">
+        <v>46255</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" s="7">
+        <v>46191</v>
+      </c>
+      <c r="S10" t="s">
+        <v>50</v>
+      </c>
+      <c r="T10" t="s">
         <v>81</v>
       </c>
-      <c r="N10">
-        <v>46255</v>
-      </c>
-      <c r="O10" t="s">
-        <v>150</v>
-      </c>
-      <c r="P10">
-        <v>46255</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>150</v>
-      </c>
-      <c r="R10">
-        <v>46191</v>
-      </c>
-      <c r="S10" t="s">
-        <v>149</v>
-      </c>
-      <c r="T10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11">
         <v>6850</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C11">
         <v>46204</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L11" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M11" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="O11" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q11" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="S11" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12">
         <v>6964</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C12">
         <v>46235</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H12" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K12" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L12" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M12" t="s">
-        <v>100</v>
-      </c>
-      <c r="N12">
+        <v>106</v>
+      </c>
+      <c r="N12" s="7">
         <v>46247</v>
       </c>
       <c r="O12" t="s">
-        <v>150</v>
-      </c>
-      <c r="P12">
+        <v>31</v>
+      </c>
+      <c r="P12" s="7">
         <v>46252</v>
       </c>
       <c r="Q12" t="s">
-        <v>150</v>
-      </c>
-      <c r="R12">
+        <v>31</v>
+      </c>
+      <c r="R12" s="7">
         <v>46245</v>
       </c>
       <c r="S12" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T12" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13">
         <v>6947</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C13">
         <v>46266</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" t="s">
         <v>102</v>
       </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" t="s">
-        <v>96</v>
-      </c>
       <c r="I13" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="J13" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="K13" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
-      </c>
-      <c r="N13">
+        <v>113</v>
+      </c>
+      <c r="N13" s="7">
         <v>46259</v>
       </c>
       <c r="O13" t="s">
-        <v>150</v>
-      </c>
-      <c r="P13">
+        <v>31</v>
+      </c>
+      <c r="P13" s="7">
         <v>46259</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="R13">
+        <v>31</v>
+      </c>
+      <c r="R13" s="7">
         <v>46245</v>
       </c>
       <c r="S13" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14">
         <v>6962</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C14">
         <v>46174</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H14" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I14" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="J14" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="K14" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M14" t="s">
-        <v>113</v>
-      </c>
-      <c r="N14">
+        <v>120</v>
+      </c>
+      <c r="N14" s="7">
         <v>46232</v>
       </c>
       <c r="O14" t="s">
-        <v>149</v>
-      </c>
-      <c r="P14">
+        <v>50</v>
+      </c>
+      <c r="P14" s="7">
         <v>46232</v>
       </c>
       <c r="Q14" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S14" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="T14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15">
         <v>6963</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C15">
         <v>46174</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I15" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="J15" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K15" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M15" t="s">
-        <v>113</v>
-      </c>
-      <c r="N15">
+        <v>120</v>
+      </c>
+      <c r="N15" s="7">
         <v>46232</v>
       </c>
       <c r="O15" t="s">
-        <v>149</v>
-      </c>
-      <c r="P15">
+        <v>50</v>
+      </c>
+      <c r="P15" s="7">
         <v>46232</v>
       </c>
       <c r="Q15" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S15" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="T15" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16">
         <v>6981</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C16">
         <v>46235</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H16" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I16" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="J16" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K16" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M16" t="s">
-        <v>123</v>
-      </c>
-      <c r="N16">
+        <v>130</v>
+      </c>
+      <c r="N16" s="7">
         <v>46233</v>
       </c>
       <c r="O16" t="s">
-        <v>150</v>
-      </c>
-      <c r="P16">
+        <v>31</v>
+      </c>
+      <c r="P16" s="7">
         <v>46233</v>
       </c>
       <c r="Q16" t="s">
-        <v>149</v>
-      </c>
-      <c r="R16">
+        <v>50</v>
+      </c>
+      <c r="R16" s="7">
         <v>46251</v>
       </c>
       <c r="S16" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T16" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17">
         <v>6974</v>
       </c>
       <c r="B17" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C17">
         <v>46204</v>
       </c>
       <c r="D17" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H17" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I17" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="J17" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K17" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="L17" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M17" t="s">
-        <v>130</v>
-      </c>
-      <c r="N17">
+        <v>137</v>
+      </c>
+      <c r="N17" s="7">
         <v>46241</v>
       </c>
       <c r="O17" t="s">
-        <v>149</v>
-      </c>
-      <c r="P17">
+        <v>50</v>
+      </c>
+      <c r="P17" s="7">
         <v>46241</v>
       </c>
       <c r="Q17" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="S17" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="T17" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18">
         <v>6949</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C18">
         <v>46204</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H18" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I18" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J18" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="K18" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M18" t="s">
-        <v>137</v>
-      </c>
-      <c r="N18">
+        <v>144</v>
+      </c>
+      <c r="N18" s="7">
         <v>46205</v>
       </c>
       <c r="O18" t="s">
-        <v>149</v>
-      </c>
-      <c r="P18">
+        <v>50</v>
+      </c>
+      <c r="P18" s="7">
         <v>46205</v>
       </c>
       <c r="Q18" t="s">
-        <v>149</v>
-      </c>
-      <c r="R18">
+        <v>50</v>
+      </c>
+      <c r="R18" s="7">
         <v>46216</v>
       </c>
       <c r="S18" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="T18" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19">
         <v>6995</v>
       </c>
       <c r="B19" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C19">
         <v>46266</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I19" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="J19" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="K19" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M19" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="O19" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q19" t="s">
-        <v>150</v>
-      </c>
-      <c r="R19">
+        <v>31</v>
+      </c>
+      <c r="R19" s="7">
         <v>46248</v>
       </c>
       <c r="S19" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="T19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20">
         <v>7005</v>
       </c>
@@ -2326,7 +2349,7 @@
         <v>157</v>
       </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
         <v>158</v>
@@ -2338,22 +2361,22 @@
         <v>160</v>
       </c>
       <c r="L20" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M20" t="s">
         <v>161</v>
       </c>
       <c r="O20" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q20" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S20" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21">
         <v>7006</v>
       </c>
@@ -2376,7 +2399,7 @@
         <v>157</v>
       </c>
       <c r="H21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I21" t="s">
         <v>163</v>
@@ -2388,22 +2411,22 @@
         <v>165</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M21" t="s">
         <v>166</v>
       </c>
       <c r="O21" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q21" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S21" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22">
         <v>7007</v>
       </c>
@@ -2426,7 +2449,7 @@
         <v>157</v>
       </c>
       <c r="H22" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s">
         <v>171</v>
@@ -2438,22 +2461,22 @@
         <v>173</v>
       </c>
       <c r="L22" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M22" t="s">
         <v>174</v>
       </c>
       <c r="O22" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q22" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S22" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23">
         <v>7012</v>
       </c>
@@ -2476,7 +2499,7 @@
         <v>157</v>
       </c>
       <c r="H23" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I23" t="s">
         <v>179</v>
@@ -2488,22 +2511,22 @@
         <v>181</v>
       </c>
       <c r="L23" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M23" t="s">
         <v>182</v>
       </c>
       <c r="O23" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q23" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S23" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24">
         <v>7012</v>
       </c>
@@ -2526,7 +2549,7 @@
         <v>157</v>
       </c>
       <c r="H24" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I24" t="s">
         <v>184</v>
@@ -2538,22 +2561,22 @@
         <v>181</v>
       </c>
       <c r="L24" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M24" t="s">
         <v>185</v>
       </c>
       <c r="O24" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q24" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S24" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25">
         <v>7014</v>
       </c>
@@ -2576,7 +2599,7 @@
         <v>157</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I25" t="s">
         <v>187</v>
@@ -2594,16 +2617,16 @@
         <v>191</v>
       </c>
       <c r="O25" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q25" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S25" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26">
         <v>7015</v>
       </c>
@@ -2626,7 +2649,7 @@
         <v>157</v>
       </c>
       <c r="H26" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s">
         <v>193</v>
@@ -2638,27 +2661,27 @@
         <v>181</v>
       </c>
       <c r="L26" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M26" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="O26" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q26" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S26" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27">
         <v>7016</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C27">
         <v>46235</v>
@@ -2667,48 +2690,48 @@
         <v>176</v>
       </c>
       <c r="E27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G27" t="s">
         <v>157</v>
       </c>
       <c r="H27" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J27" t="s">
         <v>188</v>
       </c>
       <c r="K27" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L27" t="s">
         <v>190</v>
       </c>
       <c r="M27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O27" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q27" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S27" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28">
         <v>7017</v>
       </c>
       <c r="B28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C28">
         <v>46235</v>
@@ -2726,7 +2749,7 @@
         <v>157</v>
       </c>
       <c r="H28" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s">
         <v>187</v>
@@ -2738,27 +2761,27 @@
         <v>181</v>
       </c>
       <c r="L28" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M28" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O28" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q28" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S28" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29">
         <v>7018</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C29">
         <v>46235</v>
@@ -2767,16 +2790,16 @@
         <v>176</v>
       </c>
       <c r="E29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G29" t="s">
         <v>157</v>
       </c>
       <c r="H29" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s">
         <v>184</v>
@@ -2788,27 +2811,27 @@
         <v>181</v>
       </c>
       <c r="L29" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M29" t="s">
         <v>191</v>
       </c>
       <c r="O29" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q29" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S29" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30">
         <v>7019</v>
       </c>
       <c r="B30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C30">
         <v>46235</v>
@@ -2826,7 +2849,7 @@
         <v>157</v>
       </c>
       <c r="H30" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s">
         <v>187</v>
@@ -2838,27 +2861,27 @@
         <v>181</v>
       </c>
       <c r="L30" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M30" t="s">
         <v>191</v>
       </c>
       <c r="O30" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q30" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S30" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
       <c r="A31">
         <v>7020</v>
       </c>
       <c r="B31" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C31">
         <v>46235</v>
@@ -2876,39 +2899,39 @@
         <v>157</v>
       </c>
       <c r="H31" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J31" t="s">
         <v>188</v>
       </c>
       <c r="K31" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L31" t="s">
         <v>190</v>
       </c>
       <c r="M31" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O31" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q31" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S31" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32">
         <v>7021</v>
       </c>
       <c r="B32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C32">
         <v>46235</v>
@@ -2917,57 +2940,57 @@
         <v>176</v>
       </c>
       <c r="E32" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F32" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G32" t="s">
         <v>157</v>
       </c>
       <c r="H32" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I32" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J32" t="s">
         <v>188</v>
       </c>
       <c r="K32" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L32" t="s">
         <v>190</v>
       </c>
       <c r="M32" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O32" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q32" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="S32" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" s="2">
         <v>6992</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C33" s="2">
         <v>46266</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>156</v>
@@ -2976,7 +2999,7 @@
         <v>157</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>212</v>
@@ -2988,39 +3011,39 @@
         <v>214</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>215</v>
       </c>
       <c r="O33" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q33" t="s">
-        <v>150</v>
-      </c>
-      <c r="R33">
+        <v>31</v>
+      </c>
+      <c r="R33" s="7">
         <v>46247</v>
       </c>
       <c r="S33" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" s="3">
         <v>6993</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C34" s="1">
         <v>46266</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>156</v>
@@ -3029,37 +3052,37 @@
         <v>157</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O34" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="Q34" t="s">
-        <v>150</v>
-      </c>
-      <c r="R34">
+        <v>31</v>
+      </c>
+      <c r="R34" s="7">
         <v>46247</v>
       </c>
       <c r="S34" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="30">
       <c r="A35">
         <v>6945</v>
       </c>
@@ -3082,7 +3105,7 @@
         <v>157</v>
       </c>
       <c r="H35" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>223</v>
@@ -3094,31 +3117,54 @@
         <v>225</v>
       </c>
       <c r="L35" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M35" t="s">
         <v>226</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="7">
         <v>46219</v>
       </c>
       <c r="O35" t="s">
-        <v>150</v>
-      </c>
-      <c r="P35">
+        <v>31</v>
+      </c>
+      <c r="P35" s="7">
         <v>46219</v>
       </c>
       <c r="Q35" t="s">
-        <v>150</v>
-      </c>
-      <c r="R35">
+        <v>31</v>
+      </c>
+      <c r="R35" s="7">
         <v>46217</v>
       </c>
       <c r="S35" t="s">
-        <v>150</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="6">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P1:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
+      <formula1>46023</formula1>
+      <formula2>46387</formula2>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N1:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
+      <formula1>46023</formula1>
+      <formula2>46387</formula2>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="R1:R1048576" xr:uid="{B80591A4-C609-4DDF-A9CB-595A54330A1C}">
+      <formula1>46023</formula1>
+      <formula2>46387</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O1:O6 O8:O1048576" xr:uid="{AB8A33F0-C3A3-4068-930A-A486B539D982}">
+      <formula1>"Sim;Não"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O7 Q1:Q1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
+      <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
+      <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="J4" r:id="rId1" xr:uid="{0FBB74B0-7BDF-4CCB-902E-06F540839053}"/>
     <hyperlink ref="J35" r:id="rId2" xr:uid="{66BBE0A7-BDDD-4208-88F5-EC986E31CB14}"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="391" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFDA0571-C6BB-4559-BB8F-B18A0B54658E}"/>
+  <xr:revisionPtr revIDLastSave="403" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B13C63E-435A-41CE-A305-695629CA667E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3082,7 +3082,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="30">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>6945</v>
       </c>
@@ -3143,27 +3143,25 @@
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P1:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P2:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N1:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N2:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="R1:R1048576" xr:uid="{B80591A4-C609-4DDF-A9CB-595A54330A1C}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="R2:R1048576" xr:uid="{B80591A4-C609-4DDF-A9CB-595A54330A1C}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O1:O6 O8:O1048576" xr:uid="{AB8A33F0-C3A3-4068-930A-A486B539D982}">
-      <formula1>"Sim;Não"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O7 Q1:Q1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Q2:Q1048576 O2:O1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:S1" xr:uid="{B8508FAD-82E4-46C5-AF85-D3E877D6034A}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="J4" r:id="rId1" xr:uid="{0FBB74B0-7BDF-4CCB-902E-06F540839053}"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="403" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B13C63E-435A-41CE-A305-695629CA667E}"/>
+  <xr:revisionPtr revIDLastSave="405" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85FD7B55-5A84-44E8-9D26-F791186BB2B9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3123,10 +3123,10 @@
         <v>226</v>
       </c>
       <c r="N35" s="7">
-        <v>46219</v>
+        <v>46387</v>
       </c>
       <c r="O35" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="P35" s="7">
         <v>46219</v>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="405" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85FD7B55-5A84-44E8-9D26-F791186BB2B9}"/>
+  <xr:revisionPtr revIDLastSave="407" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2967C1C-BA93-4013-A65A-41172F9891A0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3123,10 +3123,10 @@
         <v>226</v>
       </c>
       <c r="N35" s="7">
-        <v>46387</v>
+        <v>46219</v>
       </c>
       <c r="O35" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="P35" s="7">
         <v>46219</v>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="407" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2967C1C-BA93-4013-A65A-41172F9891A0}"/>
+  <xr:revisionPtr revIDLastSave="435" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0D01A31-F4CC-4BA9-A16E-53509819D70E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="253">
   <si>
     <t>ID</t>
   </si>
@@ -718,6 +718,84 @@
   </si>
   <si>
     <t>CLEY MARCOS FIDELIS;</t>
+  </si>
+  <si>
+    <t>TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t>TAITI</t>
+  </si>
+  <si>
+    <t>Joyce Cristinne - SAC;</t>
+  </si>
+  <si>
+    <t>Darlan Rodrigues;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTRADA KIZEMON TAKEUTI, Num.: 3120 Comple.: , Bairro: PARQUE SÃO JOAQUIM / </t>
+  </si>
+  <si>
+    <t>andreia.taiti@outlook.com /  financeirotaiti@outlook.com;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (11) 94889-2162 / </t>
+  </si>
+  <si>
+    <t>EZEQUIEL CLETO KEMMER;</t>
+  </si>
+  <si>
+    <t>TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDA (FILIAL 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVENIDA HELIO OSSAMU DAIKUARA , Num.: 137 Comple.: , Bairro: JARDIM VISTA ALEGRE  / </t>
+  </si>
+  <si>
+    <t>LOJA DE FABRICA PISOS E REVESTIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA DOLORES DURAN, Num.: 162 Comple.: , Bairro: JARDIM SANTO ONOFRE / </t>
+  </si>
+  <si>
+    <t>financeirotaiti@outlook.com;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">( 11) 94889-2162 / </t>
+  </si>
+  <si>
+    <t>EVALDO ELIOTERIO DE SOUZA JUNIOR;</t>
+  </si>
+  <si>
+    <t>VIASUPRI SUPRIMENTOS DE ESCRITORIO E LIMPEZA LTDA</t>
+  </si>
+  <si>
+    <t>VIASUPRI</t>
+  </si>
+  <si>
+    <t>Rogerio Egidio;</t>
+  </si>
+  <si>
+    <t>Yasmin Peixoto;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA JOSE BONIFACIO, Num.: 1853 Comple.: , Bairro: SERRARIA / </t>
+  </si>
+  <si>
+    <t>financeiro@viasupri.com.br;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 91481-5736 / </t>
+  </si>
+  <si>
+    <t>MARIA CARNEIRO BENICIO;</t>
+  </si>
+  <si>
+    <t>EXPAND COMERCIO E SERVICOS ADMINISTRATIVOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE BONIFACIO, Num.: 1853 Comple.: ANDAR 01, Bairro: SERRARIA / </t>
+  </si>
+  <si>
+    <t>MARIA SOCORRO BENÍCIO DA SILVA;</t>
   </si>
 </sst>
 </file>
@@ -779,16 +857,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -822,8 +897,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T35">
-  <autoFilter ref="A1:T35" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T40">
+  <autoFilter ref="A1:T40" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T19">
     <sortCondition ref="D1:D19"/>
   </sortState>
@@ -1170,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T35"/>
+  <dimension ref="A1:T40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
@@ -1180,20 +1255,20 @@
     <col min="5" max="5" width="16.7109375" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="19.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="7.140625" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="45.42578125" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="43.28515625" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="192" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="18" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18" style="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="27" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.7109375" style="7" customWidth="1"/>
+    <col min="18" max="18" width="17.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.85546875" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="22.85546875" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1236,19 +1311,19 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="S1" t="s">
@@ -1351,19 +1426,19 @@
       <c r="M3" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="6">
         <v>46260</v>
       </c>
       <c r="O3" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="6">
         <v>46260</v>
       </c>
       <c r="Q3" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="7">
+      <c r="R3" s="6">
         <v>46251</v>
       </c>
       <c r="S3" t="s">
@@ -1413,19 +1488,19 @@
       <c r="M4" t="s">
         <v>49</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="6">
         <v>46232</v>
       </c>
       <c r="O4" t="s">
         <v>31</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4" s="6">
         <v>46232</v>
       </c>
       <c r="Q4" t="s">
         <v>50</v>
       </c>
-      <c r="R4" s="7">
+      <c r="R4" s="6">
         <v>46253</v>
       </c>
       <c r="S4" t="s">
@@ -1466,19 +1541,19 @@
       <c r="M5" t="s">
         <v>53</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="6">
         <v>46232</v>
       </c>
       <c r="O5" t="s">
         <v>31</v>
       </c>
-      <c r="P5" s="7">
+      <c r="P5" s="6">
         <v>46232</v>
       </c>
       <c r="Q5" t="s">
         <v>50</v>
       </c>
-      <c r="R5" s="7">
+      <c r="R5" s="6">
         <v>46253</v>
       </c>
       <c r="S5" t="s">
@@ -1528,19 +1603,19 @@
       <c r="M6" t="s">
         <v>61</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="6">
         <v>46245</v>
       </c>
       <c r="O6" t="s">
         <v>31</v>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="6">
         <v>46245</v>
       </c>
       <c r="Q6" t="s">
         <v>31</v>
       </c>
-      <c r="R6" s="7">
+      <c r="R6" s="6">
         <v>46246</v>
       </c>
       <c r="S6" t="s">
@@ -1590,19 +1665,19 @@
       <c r="M7" t="s">
         <v>67</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="6">
         <v>46245</v>
       </c>
       <c r="O7" t="s">
         <v>31</v>
       </c>
-      <c r="P7" s="7">
+      <c r="P7" s="6">
         <v>46245</v>
       </c>
       <c r="Q7" t="s">
         <v>31</v>
       </c>
-      <c r="R7" s="7">
+      <c r="R7" s="6">
         <v>46246</v>
       </c>
       <c r="S7" t="s">
@@ -1658,7 +1733,7 @@
       <c r="Q8" t="s">
         <v>31</v>
       </c>
-      <c r="R8" s="7">
+      <c r="R8" s="6">
         <v>46253</v>
       </c>
       <c r="S8" t="s">
@@ -1708,19 +1783,19 @@
       <c r="M9" t="s">
         <v>80</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="6">
         <v>46255</v>
       </c>
       <c r="O9" t="s">
         <v>31</v>
       </c>
-      <c r="P9" s="7">
+      <c r="P9" s="6">
         <v>46255</v>
       </c>
       <c r="Q9" t="s">
         <v>31</v>
       </c>
-      <c r="R9" s="7">
+      <c r="R9" s="6">
         <v>46191</v>
       </c>
       <c r="S9" t="s">
@@ -1770,19 +1845,19 @@
       <c r="M10" t="s">
         <v>86</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N10" s="6">
         <v>46255</v>
       </c>
       <c r="O10" t="s">
         <v>31</v>
       </c>
-      <c r="P10" s="7">
+      <c r="P10" s="6">
         <v>46255</v>
       </c>
       <c r="Q10" t="s">
         <v>31</v>
       </c>
-      <c r="R10" s="7">
+      <c r="R10" s="6">
         <v>46191</v>
       </c>
       <c r="S10" t="s">
@@ -1885,19 +1960,19 @@
       <c r="M12" t="s">
         <v>106</v>
       </c>
-      <c r="N12" s="7">
+      <c r="N12" s="6">
         <v>46247</v>
       </c>
       <c r="O12" t="s">
         <v>31</v>
       </c>
-      <c r="P12" s="7">
+      <c r="P12" s="6">
         <v>46252</v>
       </c>
       <c r="Q12" t="s">
         <v>31</v>
       </c>
-      <c r="R12" s="7">
+      <c r="R12" s="6">
         <v>46245</v>
       </c>
       <c r="S12" t="s">
@@ -1947,19 +2022,19 @@
       <c r="M13" t="s">
         <v>113</v>
       </c>
-      <c r="N13" s="7">
+      <c r="N13" s="6">
         <v>46259</v>
       </c>
       <c r="O13" t="s">
         <v>31</v>
       </c>
-      <c r="P13" s="7">
+      <c r="P13" s="6">
         <v>46259</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R13" s="7">
+      <c r="R13" s="6">
         <v>46245</v>
       </c>
       <c r="S13" t="s">
@@ -2009,13 +2084,13 @@
       <c r="M14" t="s">
         <v>120</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N14" s="6">
         <v>46232</v>
       </c>
       <c r="O14" t="s">
         <v>50</v>
       </c>
-      <c r="P14" s="7">
+      <c r="P14" s="6">
         <v>46232</v>
       </c>
       <c r="Q14" t="s">
@@ -2068,13 +2143,13 @@
       <c r="M15" t="s">
         <v>120</v>
       </c>
-      <c r="N15" s="7">
+      <c r="N15" s="6">
         <v>46232</v>
       </c>
       <c r="O15" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="7">
+      <c r="P15" s="6">
         <v>46232</v>
       </c>
       <c r="Q15" t="s">
@@ -2127,19 +2202,19 @@
       <c r="M16" t="s">
         <v>130</v>
       </c>
-      <c r="N16" s="7">
+      <c r="N16" s="6">
         <v>46233</v>
       </c>
       <c r="O16" t="s">
         <v>31</v>
       </c>
-      <c r="P16" s="7">
+      <c r="P16" s="6">
         <v>46233</v>
       </c>
       <c r="Q16" t="s">
         <v>50</v>
       </c>
-      <c r="R16" s="7">
+      <c r="R16" s="6">
         <v>46251</v>
       </c>
       <c r="S16" t="s">
@@ -2189,13 +2264,13 @@
       <c r="M17" t="s">
         <v>137</v>
       </c>
-      <c r="N17" s="7">
+      <c r="N17" s="6">
         <v>46241</v>
       </c>
       <c r="O17" t="s">
         <v>50</v>
       </c>
-      <c r="P17" s="7">
+      <c r="P17" s="6">
         <v>46241</v>
       </c>
       <c r="Q17" t="s">
@@ -2248,19 +2323,19 @@
       <c r="M18" t="s">
         <v>144</v>
       </c>
-      <c r="N18" s="7">
+      <c r="N18" s="6">
         <v>46205</v>
       </c>
       <c r="O18" t="s">
         <v>50</v>
       </c>
-      <c r="P18" s="7">
+      <c r="P18" s="6">
         <v>46205</v>
       </c>
       <c r="Q18" t="s">
         <v>50</v>
       </c>
-      <c r="R18" s="7">
+      <c r="R18" s="6">
         <v>46216</v>
       </c>
       <c r="S18" t="s">
@@ -2316,7 +2391,7 @@
       <c r="Q19" t="s">
         <v>31</v>
       </c>
-      <c r="R19" s="7">
+      <c r="R19" s="6">
         <v>46248</v>
       </c>
       <c r="S19" t="s">
@@ -3022,7 +3097,7 @@
       <c r="Q33" t="s">
         <v>31</v>
       </c>
-      <c r="R33" s="7">
+      <c r="R33" s="6">
         <v>46247</v>
       </c>
       <c r="S33" t="s">
@@ -3075,79 +3150,352 @@
       <c r="Q34" t="s">
         <v>31</v>
       </c>
-      <c r="R34" s="7">
+      <c r="R34" s="6">
         <v>46247</v>
       </c>
       <c r="S34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
-      <c r="A35">
+    <row r="35" spans="1:19" ht="17.25" customHeight="1">
+      <c r="A35" s="3">
         <v>6945</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>221</v>
       </c>
       <c r="C35" s="1">
         <v>46174</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="1" t="s">
         <v>223</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K35" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="L35" t="s">
+      <c r="L35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M35" t="s">
+      <c r="M35" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="N35" s="7">
+      <c r="N35" s="6">
         <v>46219</v>
       </c>
       <c r="O35" t="s">
         <v>31</v>
       </c>
-      <c r="P35" s="7">
+      <c r="P35" s="6">
         <v>46219</v>
       </c>
       <c r="Q35" t="s">
         <v>31</v>
       </c>
-      <c r="R35" s="7">
+      <c r="R35" s="6">
         <v>46217</v>
       </c>
       <c r="S35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="17.25" customHeight="1">
+      <c r="A36" s="3">
+        <v>6915</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N36" s="6">
+        <v>46168</v>
+      </c>
+      <c r="O36" t="s">
+        <v>50</v>
+      </c>
+      <c r="P36" s="6">
+        <v>46168</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>50</v>
+      </c>
+      <c r="R36" s="6">
+        <v>46163</v>
+      </c>
+      <c r="S36" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" s="3">
+        <v>6916</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N37" s="6">
+        <v>46168</v>
+      </c>
+      <c r="O37" t="s">
+        <v>50</v>
+      </c>
+      <c r="P37" s="6">
+        <v>46168</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>50</v>
+      </c>
+      <c r="R37" s="6">
+        <v>46163</v>
+      </c>
+      <c r="S37" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" s="3">
+        <v>6917</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" s="1">
+        <v>46174</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="N38" s="6">
+        <v>46168</v>
+      </c>
+      <c r="O38" t="s">
+        <v>50</v>
+      </c>
+      <c r="P38" s="6">
+        <v>46168</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>50</v>
+      </c>
+      <c r="R38" s="6">
+        <v>46163</v>
+      </c>
+      <c r="S38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" s="3">
+        <v>7036</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="O39" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>31</v>
+      </c>
+      <c r="S39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" s="3">
+        <v>7037</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C40" s="1">
+        <v>46266</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="O40" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>31</v>
+      </c>
+      <c r="S40" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P2:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
-      <formula1>46023</formula1>
-      <formula2>46387</formula2>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N2:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="N36:N38 P2:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
@@ -3155,13 +3503,17 @@
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Q2:Q1048576 O2:O1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="S36:S40 Q2:Q1048576 O2:O1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S35 S41:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:S1" xr:uid="{B8508FAD-82E4-46C5-AF85-D3E877D6034A}"/>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N2:N35 N41:N1048576 M36:M40" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
+      <formula1>46023</formula1>
+      <formula2>46387</formula2>
+    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="J4" r:id="rId1" xr:uid="{0FBB74B0-7BDF-4CCB-902E-06F540839053}"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="435" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0D01A31-F4CC-4BA9-A16E-53509819D70E}"/>
+  <xr:revisionPtr revIDLastSave="439" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBA9CE76-72B9-463F-8C14-CC96AEEFB485}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="238">
   <si>
     <t>ID</t>
   </si>
@@ -718,51 +718,6 @@
   </si>
   <si>
     <t>CLEY MARCOS FIDELIS;</t>
-  </si>
-  <si>
-    <t>TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDA</t>
-  </si>
-  <si>
-    <t>TAITI</t>
-  </si>
-  <si>
-    <t>Joyce Cristinne - SAC;</t>
-  </si>
-  <si>
-    <t>Darlan Rodrigues;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTRADA KIZEMON TAKEUTI, Num.: 3120 Comple.: , Bairro: PARQUE SÃO JOAQUIM / </t>
-  </si>
-  <si>
-    <t>andreia.taiti@outlook.com /  financeirotaiti@outlook.com;</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (11) 94889-2162 / </t>
-  </si>
-  <si>
-    <t>EZEQUIEL CLETO KEMMER;</t>
-  </si>
-  <si>
-    <t>TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDA (FILIAL 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVENIDA HELIO OSSAMU DAIKUARA , Num.: 137 Comple.: , Bairro: JARDIM VISTA ALEGRE  / </t>
-  </si>
-  <si>
-    <t>LOJA DE FABRICA PISOS E REVESTIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA DOLORES DURAN, Num.: 162 Comple.: , Bairro: JARDIM SANTO ONOFRE / </t>
-  </si>
-  <si>
-    <t>financeirotaiti@outlook.com;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">( 11) 94889-2162 / </t>
-  </si>
-  <si>
-    <t>EVALDO ELIOTERIO DE SOUZA JUNIOR;</t>
   </si>
   <si>
     <t>VIASUPRI SUPRIMENTOS DE ESCRITORIO E LIMPEZA LTDA</t>
@@ -897,8 +852,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T40">
-  <autoFilter ref="A1:T40" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:T37">
+  <autoFilter ref="A1:T37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T19">
     <sortCondition ref="D1:D19"/>
   </sortState>
@@ -1245,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
@@ -1961,7 +1916,7 @@
         <v>106</v>
       </c>
       <c r="N12" s="6">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="O12" t="s">
         <v>31</v>
@@ -2203,7 +2158,7 @@
         <v>130</v>
       </c>
       <c r="N16" s="6">
-        <v>46233</v>
+        <v>46253</v>
       </c>
       <c r="O16" t="s">
         <v>31</v>
@@ -2385,6 +2340,9 @@
       <c r="M19" t="s">
         <v>151</v>
       </c>
+      <c r="N19" s="6">
+        <v>46252</v>
+      </c>
       <c r="O19" t="s">
         <v>31</v>
       </c>
@@ -3216,27 +3174,27 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="17.25" customHeight="1">
+    <row r="36" spans="1:19">
       <c r="A36" s="3">
-        <v>6915</v>
+        <v>7036</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>227</v>
       </c>
       <c r="C36" s="1">
-        <v>46174</v>
+        <v>46266</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>228</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>102</v>
@@ -3256,49 +3214,40 @@
       <c r="M36" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="N36" s="6">
-        <v>46168</v>
-      </c>
       <c r="O36" t="s">
-        <v>50</v>
-      </c>
-      <c r="P36" s="6">
-        <v>46168</v>
+        <v>31</v>
       </c>
       <c r="Q36" t="s">
-        <v>50</v>
-      </c>
-      <c r="R36" s="6">
-        <v>46163</v>
+        <v>31</v>
       </c>
       <c r="S36" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:19">
       <c r="A37" s="3">
-        <v>6916</v>
+        <v>7037</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>235</v>
       </c>
       <c r="C37" s="1">
-        <v>46174</v>
+        <v>46266</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>228</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>236</v>
@@ -3313,189 +3262,29 @@
         <v>60</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="N37" s="6">
-        <v>46168</v>
+        <v>237</v>
       </c>
       <c r="O37" t="s">
-        <v>50</v>
-      </c>
-      <c r="P37" s="6">
-        <v>46168</v>
+        <v>31</v>
       </c>
       <c r="Q37" t="s">
-        <v>50</v>
-      </c>
-      <c r="R37" s="6">
-        <v>46163</v>
+        <v>31</v>
       </c>
       <c r="S37" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19">
-      <c r="A38" s="3">
-        <v>6917</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C38" s="1">
-        <v>46174</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="N38" s="6">
-        <v>46168</v>
-      </c>
-      <c r="O38" t="s">
-        <v>50</v>
-      </c>
-      <c r="P38" s="6">
-        <v>46168</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>50</v>
-      </c>
-      <c r="R38" s="6">
-        <v>46163</v>
-      </c>
-      <c r="S38" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19">
-      <c r="A39" s="3">
-        <v>7036</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C39" s="1">
-        <v>46266</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="O39" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>31</v>
-      </c>
-      <c r="S39" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19">
-      <c r="A40" s="3">
-        <v>7037</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C40" s="1">
-        <v>46266</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="O40" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>31</v>
-      </c>
-      <c r="S40" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="N36:N38 P2:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S35 S38:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
+      <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:S1" xr:uid="{B8508FAD-82E4-46C5-AF85-D3E877D6034A}"/>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N2:N35 N38:N1048576 M36:M37" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
+      <formula1>46023</formula1>
+      <formula2>46387</formula2>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P2:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
@@ -3503,16 +3292,8 @@
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="S36:S40 Q2:Q1048576 O2:O1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="S36:S37 O2:O1048576 Q2:Q1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
       <formula1>"Sim,Não"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S35 S41:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
-      <formula1>"Sim,Não"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:S1" xr:uid="{B8508FAD-82E4-46C5-AF85-D3E877D6034A}"/>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N2:N35 N41:N1048576 M36:M40" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
-      <formula1>46023</formula1>
-      <formula2>46387</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="439" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBA9CE76-72B9-463F-8C14-CC96AEEFB485}"/>
+  <xr:revisionPtr revIDLastSave="476" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{141A61D8-F7A0-4B6B-BE4B-4D9EC53386BF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,7 +128,7 @@
     <t>Industria</t>
   </si>
   <si>
-    <t>RAFAELA YUMI TUKAMOTO;</t>
+    <t>RAFAELA YUMI TUKAMOTO (Sócio);</t>
   </si>
   <si>
     <t>Não</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">(11) 95463-2059 / </t>
   </si>
   <si>
-    <t>DANIEL DE JESUS LOPES;</t>
+    <t>DANIEL DE JESUS LOPES (Sócio);</t>
   </si>
   <si>
     <t>djl</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">(32) 98839-2048 / </t>
   </si>
   <si>
-    <t>JACINTO DE OLIVEIRA NETO;CÁRITAS NEIVA VIEIRA FRANÇA;</t>
+    <t>JACINTO DE OLIVEIRA NETO;CÁRITAS NEIVA VIEIRA FRANÇA (Sócio);</t>
   </si>
   <si>
     <t>Sim</t>
@@ -197,7 +197,7 @@
     <t>PROTECTION SHIELD LTDA</t>
   </si>
   <si>
-    <t>CÁRITAS NEIVA VIEIRA FRANÇA;</t>
+    <t>CÁRITAS NEIVA VIEIRA FRANÇA (Sócio);</t>
   </si>
   <si>
     <t>HELBRAZ COMERCIO DE PAPELARIA LTDA</t>
@@ -221,7 +221,7 @@
     <t>Varejo</t>
   </si>
   <si>
-    <t>CLAUDIA HELENA DE OLIVEIRA RODRIGUES LUCENA;</t>
+    <t>CLAUDIA HELENA DE OLIVEIRA RODRIGUES LUCENA (Sócio);</t>
   </si>
   <si>
     <t>helbraz</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">(62) 99291-1415 / </t>
   </si>
   <si>
-    <t>ANTONIO JUSTINO LUCENA FILHO;</t>
+    <t>ANTONIO JUSTINO LUCENA FILHO (Sócio);</t>
   </si>
   <si>
     <t>HEPA FILTROS LTDA</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">(11) 98452-3000 / </t>
   </si>
   <si>
-    <t>EDIMO RODRIGUES DA MATA;</t>
+    <t>EDIMO RODRIGUES DA MATA (Sócio);</t>
   </si>
   <si>
     <t>hepa-filtros</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">(11) 4767-7868 / </t>
   </si>
   <si>
-    <t>GENILDO FRANCISCO DA SILVA;</t>
+    <t>GENILDO FRANCISCO DA SILVA (Sócio);</t>
   </si>
   <si>
     <t>jgtec</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">(11) 98924-3309 / </t>
   </si>
   <si>
-    <t>MILENA CELESTINO DA SILVA;</t>
+    <t>MILENA CELESTINO DA SILVA (Sócio);</t>
   </si>
   <si>
     <t>J R BARROS COMERCIO LTDA</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">(19) 3858-1024 / </t>
   </si>
   <si>
-    <t>JOEL CHERUBIM DE BARROS;</t>
+    <t>JOEL CHERUBIM DE BARROS (Sócio);</t>
   </si>
   <si>
     <t>lagoa-bonita</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">(11) 9 8492-0187 / </t>
   </si>
   <si>
-    <t>JANDUI RODRIGUES DE MIRANDA; FELIPE DIJAN SANTOS DE MIRANDA;</t>
+    <t>JANDUI RODRIGUES DE MIRANDA; FELIPE DIJAN SANTOS DE MIRANDA (Sócio);</t>
   </si>
   <si>
     <t>mercado-dijan</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">(11) 971076-459 / </t>
   </si>
   <si>
-    <t>FRANCISCO MARQUES DE SA;</t>
+    <t>FRANCISCO MARQUES DE SA (Sócio);</t>
   </si>
   <si>
     <t>mileto</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">(62) 98248-1809 / </t>
   </si>
   <si>
-    <t>MAYARA MODENA ;</t>
+    <t>MAYARA MODENA (Sócio);</t>
   </si>
   <si>
     <t>promotoras-gyn</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">(62) 3374-6330 / </t>
   </si>
   <si>
-    <t>LUIZ GOMES DA SILVA;</t>
+    <t>LUIZ GOMES DA SILVA (Sócio);</t>
   </si>
   <si>
     <t>supermercado-avenida</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">(83) 99380-9989 / </t>
   </si>
   <si>
-    <t>FRANCINALDO FERREIRA DE ANDRADE;</t>
+    <t>FRANCINALDO FERREIRA DE ANDRADE (Sócio);</t>
   </si>
   <si>
     <t>supermercado-nana</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">(62) 98188-8476 / </t>
   </si>
   <si>
-    <t>ANGELA FERNANDA MENDONÇA DE ARAUJO,;</t>
+    <t>ANGELA FERNANDA MENDONÇA DE ARAUJO (Sócio);</t>
   </si>
   <si>
     <t>tec-grua</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">(34)99231-9350 / </t>
   </si>
   <si>
-    <t>THAINA CRISTINA PEREIRA;</t>
+    <t>THAINA CRISTINA PEREIRA (Sócio);</t>
   </si>
   <si>
     <t>trizga</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">(11) 91648-5026 / </t>
   </si>
   <si>
-    <t>GABRIEL PALADINO RAUNAIMER; BRUNO PALADINO RAUNAIMER;</t>
+    <t>GABRIEL PALADINO RAUNAIMER (Sócio); BRUNO PALADINO RAUNAIMER (Sócio);</t>
   </si>
   <si>
     <t>RK - INDUSTRIA E COMERCIO DE PLASTICOS LTDA</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">11 91648-5026 / </t>
   </si>
   <si>
-    <t>SERGIO TADEU RAUNAIMER;ELAINE APARECIDA MOLINARI ZAMORA;</t>
+    <t>SERGIO TADEU RAUNAIMER (Sócio); ELAINE APARECIDA MOLINARI ZAMORA (Sócio);</t>
   </si>
   <si>
     <t>SANTOS &amp; DIAN MATERIAIS PARA CONSTRUCAO LTDA</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">(11) 4582-5121 / </t>
   </si>
   <si>
-    <t>WILSON APARECIDO DIAN;</t>
+    <t>WILSON APARECIDO DIAN (Sócio);</t>
   </si>
   <si>
     <t>COMERCIO VAREJISTA DE MERCADORIAS 3M LTDA (MATRIZ)</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">11 5832-2100 Ramal 229 - Cel: 11 95911-9371 / </t>
   </si>
   <si>
-    <t>AA&amp;amp;MARTINS PARTICIPACOES LTDA;ADRIANO AUGUSTO MARTINS;E&amp;amp;G MARTINS PARTICIPACOES LTDA;EDUARDO DE JESUS MARTINS; B&amp;amp;SOLAR PARTICIPACOES LTDA;MARCOS MARQUES MARTINS;</t>
+    <t>AA&amp;amp;MARTINS PARTICIPACOES LTDA (Sócio);ADRIANO AUGUSTO MARTINS;E&amp;amp;G MARTINS PARTICIPACOES LTDA;EDUARDO DE JESUS MARTINS; B&amp;amp;SOLAR PARTICIPACOES LTDA;MARCOS MARQUES MARTINS;</t>
   </si>
   <si>
     <t>COMERCIO VAREJISTA DE MERCADORIAS 3M LTDA (FILIAL 1)</t>
@@ -1201,29 +1201,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="26.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="45.42578125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="43.28515625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="192" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="27" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.85546875" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" customWidth="1"/>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" customWidth="1"/>
+    <col min="9" max="9" width="7.140625" customWidth="1"/>
+    <col min="10" max="10" width="45.42578125" customWidth="1"/>
+    <col min="11" max="11" width="43.28515625" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" customWidth="1"/>
+    <col min="13" max="13" width="192" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="6" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="6" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1919,7 +1916,7 @@
         <v>46252</v>
       </c>
       <c r="O12" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="P12" s="6">
         <v>46252</v>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="476" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{141A61D8-F7A0-4B6B-BE4B-4D9EC53386BF}"/>
+  <xr:revisionPtr revIDLastSave="491" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C87AE8-FC9E-4E6F-90AD-91DFE3114A68}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">11 5832-2100 Ramal 229 - Cel: 11 95911-9371 / </t>
   </si>
   <si>
-    <t>AA&amp;amp;MARTINS PARTICIPACOES LTDA (Sócio);ADRIANO AUGUSTO MARTINS;E&amp;amp;G MARTINS PARTICIPACOES LTDA;EDUARDO DE JESUS MARTINS; B&amp;amp;SOLAR PARTICIPACOES LTDA;MARCOS MARQUES MARTINS;</t>
+    <t>AA&amp;amp;MARTINS PARTICIPACOES LTDA (Sócio);ADRIANO AUGUSTO MARTINS (Sócio);E&amp;amp;G MARTINS PARTICIPACOES LTDA (Sócio);EDUARDO DE JESUS MARTINS (Sócio) ; B&amp;amp;SOLAR PARTICIPACOES LTDA (Sócio);MARCOS MARQUES MARTINS (Sócio);</t>
   </si>
   <si>
     <t>COMERCIO VAREJISTA DE MERCADORIAS 3M LTDA (FILIAL 1)</t>
@@ -611,7 +611,7 @@
     <t>Holding</t>
   </si>
   <si>
-    <t>MARCOS MARQUES MARTINS;</t>
+    <t>MARCOS MARQUES MARTINS (Sócio);</t>
   </si>
   <si>
     <t>FRUTAS DA TERRA HORTIFRUTI LTDA</t>
@@ -623,7 +623,7 @@
     <t>contabil@supermercados3m.com.br;</t>
   </si>
   <si>
-    <t>E&amp;amp;G MARTINS PARTICIPACOES LTDA;EDUARDO DE JESUS MARTINS; AA&amp;amp;MARTINS PARTICIPACOES LTDA;ADRIANO AUGUSTO MARTINS; B&amp;amp;SOLAR PARTICIPACOES LTDA;MARCOS MARQUES MARTINS;</t>
+    <t>E&amp;amp;G MARTINS PARTICIPACOES LTDA (Sócio);EDUARDO DE JESUS MARTINS (Sócio); AA&amp;amp;MARTINS PARTICIPACOES LTDA (Sócio);ADRIANO AUGUSTO MARTINS (Sócio); B&amp;amp;SOLAR PARTICIPACOES LTDA (Sócio);MARCOS MARQUES MARTINS (Sócio);</t>
   </si>
   <si>
     <t>E&amp;G MARTINS PARTICIPAÇÕES LTDA</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">(11) 4741-0807 / </t>
   </si>
   <si>
-    <t>EDUARDO DE JESUS MARTINS;</t>
+    <t>EDUARDO DE JESUS MARTINS (Sócio);</t>
   </si>
   <si>
     <t>E&amp;G MARTINS ADMINISTRACAO DE BENS PROPRIOS LTDA</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">Avenida Giovanni Gronchi, Num.: 6195 Comple.: Sala 13, Bairro: Vila Andrade / </t>
   </si>
   <si>
-    <t>ADRIANO AUGUSTO MARTINS;</t>
+    <t>ADRIANO AUGUSTO MARTINS (Sócio);</t>
   </si>
   <si>
     <t>AA&amp;MARTINS PARTICIPACOES LTDA</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">64 996444975 / </t>
   </si>
   <si>
-    <t>ALDENIR VENANCIO DE OLIVEIRA;</t>
+    <t>ALDENIR VENANCIO DE OLIVEIRA (Sócio);</t>
   </si>
   <si>
     <t>GOMES SERVIÇOS - LTDA</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">(64) 99647-7060 / </t>
   </si>
   <si>
-    <t>ARMANDO GOMES DE ASSIS;</t>
+    <t>ARMANDO GOMES DE ASSIS (Sócio);</t>
   </si>
   <si>
     <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
@@ -717,7 +717,7 @@
     <t>(62) 8180-4195 /</t>
   </si>
   <si>
-    <t>CLEY MARCOS FIDELIS;</t>
+    <t>CLEY MARCOS FIDELIS (Sócio);</t>
   </si>
   <si>
     <t>VIASUPRI SUPRIMENTOS DE ESCRITORIO E LIMPEZA LTDA</t>
@@ -741,7 +741,7 @@
     <t xml:space="preserve">(11) 91481-5736 / </t>
   </si>
   <si>
-    <t>MARIA CARNEIRO BENICIO;</t>
+    <t xml:space="preserve">MARIA CARNEIRO BENICIO (Sócio); </t>
   </si>
   <si>
     <t>EXPAND COMERCIO E SERVICOS ADMINISTRATIVOS LTDA</t>
@@ -750,7 +750,7 @@
     <t xml:space="preserve">JOSE BONIFACIO, Num.: 1853 Comple.: ANDAR 01, Bairro: SERRARIA / </t>
   </si>
   <si>
-    <t>MARIA SOCORRO BENÍCIO DA SILVA;</t>
+    <t>MARIA SOCORRO BENÍCIO DA SILVA (Sócio);</t>
   </si>
 </sst>
 </file>
@@ -1203,24 +1203,26 @@
   <dimension ref="A1:T37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" customWidth="1"/>
-    <col min="8" max="8" width="26.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.140625" customWidth="1"/>
-    <col min="10" max="10" width="45.42578125" customWidth="1"/>
-    <col min="11" max="11" width="43.28515625" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" customWidth="1"/>
-    <col min="13" max="13" width="192" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="6" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="6" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="6" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="118.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="42.42578125" customWidth="1"/>
+    <col min="14" max="14" width="18.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -3276,8 +3278,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S35 S38:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:S1" xr:uid="{B8508FAD-82E4-46C5-AF85-D3E877D6034A}"/>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N2:N35 N38:N1048576 M36:M37" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:S1 M36:M37" xr:uid="{B8508FAD-82E4-46C5-AF85-D3E877D6034A}"/>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N2:N35 N38:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="491" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C87AE8-FC9E-4E6F-90AD-91DFE3114A68}"/>
+  <xr:revisionPtr revIDLastSave="495" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10803FAA-A6C5-4B6B-A666-2553739606C4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">(32) 98839-2048 / </t>
   </si>
   <si>
-    <t>JACINTO DE OLIVEIRA NETO;CÁRITAS NEIVA VIEIRA FRANÇA (Sócio);</t>
+    <t>JACINTO DE OLIVEIRA NETO (Sócio) ; CÁRITAS NEIVA VIEIRA FRANÇA (Sócio);</t>
   </si>
   <si>
     <t>Sim</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">(11) 9 8492-0187 / </t>
   </si>
   <si>
-    <t>JANDUI RODRIGUES DE MIRANDA; FELIPE DIJAN SANTOS DE MIRANDA (Sócio);</t>
+    <t>JANDUI RODRIGUES DE MIRANDA (Sócio); FELIPE DIJAN SANTOS DE MIRANDA (Sócio);</t>
   </si>
   <si>
     <t>mercado-dijan</t>
@@ -1215,7 +1215,7 @@
     <col min="10" max="10" width="46.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="44.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="42.42578125" customWidth="1"/>
+    <col min="13" max="13" width="93.7109375" customWidth="1"/>
     <col min="14" max="14" width="18.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="29" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17.140625" style="6" bestFit="1" customWidth="1"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="533" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{669A74E5-C6DC-4FEA-AA11-70DE6BFE6069}"/>
+  <xr:revisionPtr revIDLastSave="543" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00A8E097-DB71-4D9B-8D07-CBF5DE8365A9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="235">
   <si>
     <t>ID</t>
   </si>
@@ -724,6 +724,15 @@
   </si>
   <si>
     <t xml:space="preserve">MARIA CARNEIRO BENICIO ; </t>
+  </si>
+  <si>
+    <t>Aline</t>
+  </si>
+  <si>
+    <t>financeiro@viasupri.com.br</t>
+  </si>
+  <si>
+    <t>(11) 9181-5736</t>
   </si>
   <si>
     <t>EXPAND COMERCIO E SERVICOS ADMINISTRATIVOS LTDA</t>
@@ -739,7 +748,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -766,6 +775,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -907,7 +922,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -933,6 +948,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -3948,9 +3964,15 @@
       <c r="O36" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
+      <c r="P36" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="R36" s="5" t="s">
+        <v>231</v>
+      </c>
       <c r="S36" s="5"/>
       <c r="T36" s="5" t="s">
         <v>39</v>
@@ -3971,7 +3993,7 @@
         <v>7037</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C37" s="19">
         <v>46266</v>
@@ -3992,7 +4014,7 @@
         <v>33</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J37" s="19" t="s">
         <v>226</v>
@@ -4004,15 +4026,21 @@
         <v>65</v>
       </c>
       <c r="M37" s="19" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N37" s="19"/>
       <c r="O37" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
+      <c r="P37" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="R37" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S37" s="19"/>
       <c r="T37" s="19" t="s">
         <v>39</v>
@@ -4052,10 +4080,12 @@
   <hyperlinks>
     <hyperlink ref="J4" r:id="rId1" xr:uid="{CA01C30A-1B80-4AE9-9E03-14A994B515F0}"/>
     <hyperlink ref="J35" r:id="rId2" xr:uid="{2C71ACE8-F29E-423C-AC01-4FFAE1F9088D}"/>
+    <hyperlink ref="Q36" r:id="rId3" xr:uid="{E698CFD6-B238-46F2-B3C1-0504D5AFD533}"/>
+    <hyperlink ref="Q37" r:id="rId4" xr:uid="{7A13F7C7-377F-4FEF-8EE6-CBF954B876C0}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="543" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00A8E097-DB71-4D9B-8D07-CBF5DE8365A9}"/>
+  <xr:revisionPtr revIDLastSave="545" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67B25243-9F31-4617-89BF-3154FF60134F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="234">
   <si>
     <t>ID</t>
   </si>
@@ -174,9 +174,6 @@
   </si>
   <si>
     <t xml:space="preserve">RUA ARISUGAWA, Num.: 206 Comple.: , Bairro: JARDIM JAPÃO / </t>
-  </si>
-  <si>
-    <t>;</t>
   </si>
   <si>
     <t xml:space="preserve">(11) 95463-2059 / </t>
@@ -1814,17 +1811,15 @@
       <c r="I3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="7"/>
+      <c r="K3" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N3" s="8">
         <v>46260</v>
@@ -1859,13 +1854,13 @@
         <v>6976</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="5">
         <v>46235</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>42</v>
@@ -1874,25 +1869,25 @@
         <v>43</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>37</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4" s="10">
         <v>46232</v>
@@ -1907,7 +1902,7 @@
         <v>46232</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
@@ -1927,13 +1922,13 @@
         <v>6977</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" s="7">
         <v>46235</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>42</v>
@@ -1942,7 +1937,7 @@
         <v>43</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>33</v>
@@ -1954,7 +1949,7 @@
         <v>37</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N5" s="8">
         <v>46232</v>
@@ -1969,7 +1964,7 @@
         <v>46232</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -1989,40 +1984,40 @@
         <v>6966</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="5">
         <v>46235</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="N6" s="10">
         <v>46245</v>
@@ -2057,40 +2052,40 @@
         <v>6967</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" s="7">
         <v>46235</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="K7" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="L7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="N7" s="8">
         <v>46245</v>
@@ -2125,13 +2120,13 @@
         <v>6978</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="5">
         <v>46266</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>42</v>
@@ -2140,25 +2135,25 @@
         <v>43</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>37</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5" t="s">
@@ -2189,13 +2184,13 @@
         <v>6923</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" s="7">
         <v>46204</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>42</v>
@@ -2210,19 +2205,19 @@
         <v>33</v>
       </c>
       <c r="I9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="K9" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N9" s="8">
         <v>46255</v>
@@ -2246,7 +2241,7 @@
         <v>46191</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z9" s="7"/>
       <c r="AA9" s="7"/>
@@ -2257,13 +2252,13 @@
         <v>6924</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="5">
         <v>46204</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>42</v>
@@ -2278,19 +2273,19 @@
         <v>33</v>
       </c>
       <c r="I10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>37</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N10" s="10">
         <v>46255</v>
@@ -2314,7 +2309,7 @@
         <v>46191</v>
       </c>
       <c r="Y10" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z10" s="5"/>
       <c r="AA10" s="5"/>
@@ -2325,40 +2320,40 @@
         <v>6850</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" s="7">
         <v>46204</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="I11" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="L11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7" t="s">
@@ -2369,7 +2364,7 @@
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -2387,46 +2382,46 @@
         <v>6964</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C12" s="5">
         <v>46235</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="J12" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="K12" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="L12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M12" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="N12" s="10">
         <v>46252</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
@@ -2455,13 +2450,13 @@
         <v>6947</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" s="7">
         <v>46266</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>42</v>
@@ -2470,25 +2465,25 @@
         <v>43</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="K13" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>112</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N13" s="8">
         <v>46259</v>
@@ -2523,46 +2518,46 @@
         <v>6962</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C14" s="5">
         <v>46174</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J14" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="K14" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>37</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N14" s="10">
         <v>46232</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
@@ -2578,7 +2573,7 @@
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z14" s="5"/>
       <c r="AA14" s="5"/>
@@ -2589,46 +2584,46 @@
         <v>6963</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C15" s="7">
         <v>46174</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>43</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>122</v>
-      </c>
       <c r="K15" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N15" s="8">
         <v>46232</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
@@ -2644,7 +2639,7 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z15" s="7"/>
       <c r="AA15" s="7"/>
@@ -2655,40 +2650,40 @@
         <v>6981</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C16" s="5">
         <v>46235</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I16" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="K16" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="L16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="N16" s="10">
         <v>46253</v>
@@ -2703,7 +2698,7 @@
         <v>46233</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
@@ -2723,46 +2718,46 @@
         <v>6974</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C17" s="7">
         <v>46204</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>43</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="K17" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="L17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="7" t="s">
         <v>133</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>134</v>
       </c>
       <c r="N17" s="8">
         <v>46241</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
@@ -2771,14 +2766,14 @@
         <v>46241</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z17" s="7"/>
       <c r="AA17" s="7"/>
@@ -2789,46 +2784,46 @@
         <v>6949</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="5">
         <v>46204</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I18" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="K18" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>37</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N18" s="10">
         <v>46205</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
@@ -2837,7 +2832,7 @@
         <v>46205</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
@@ -2846,7 +2841,7 @@
         <v>46216</v>
       </c>
       <c r="Y18" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
@@ -2857,40 +2852,40 @@
         <v>6995</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C19" s="7">
         <v>46266</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>42</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I19" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="K19" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N19" s="8">
         <v>46252</v>
@@ -2923,40 +2918,40 @@
         <v>7005</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" s="5">
         <v>46266</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I20" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="K20" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>154</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>37</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5" t="s">
@@ -2985,40 +2980,40 @@
         <v>7006</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C21" s="7">
         <v>46266</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="F21" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="G21" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I21" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="K21" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>159</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N21" s="7"/>
       <c r="O21" s="7" t="s">
@@ -3047,40 +3042,40 @@
         <v>7007</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C22" s="5">
         <v>46266</v>
       </c>
       <c r="D22" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I22" s="5" t="s">
+      <c r="J22" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="K22" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="L22" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M22" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5" t="s">
@@ -3109,40 +3104,40 @@
         <v>7012</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="7">
         <v>46235</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="G23" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="I23" s="7" t="s">
+      <c r="J23" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="K23" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="L23" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M23" s="7" t="s">
         <v>175</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>176</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="7" t="s">
@@ -3171,40 +3166,40 @@
         <v>7012</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C24" s="5">
         <v>46235</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>172</v>
-      </c>
       <c r="G24" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I24" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M24" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="N24" s="13"/>
       <c r="O24" s="5" t="s">
@@ -3233,40 +3228,40 @@
         <v>7014</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C25" s="7">
         <v>46235</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>172</v>
-      </c>
       <c r="G25" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I25" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="K25" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="K25" s="7" t="s">
+      <c r="L25" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="M25" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="N25" s="7"/>
       <c r="O25" s="7" t="s">
@@ -3295,40 +3290,40 @@
         <v>7015</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C26" s="5">
         <v>46235</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>172</v>
-      </c>
       <c r="G26" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I26" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="K26" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M26" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="N26" s="13"/>
       <c r="O26" s="5" t="s">
@@ -3357,40 +3352,40 @@
         <v>7016</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C27" s="7">
         <v>46235</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E27" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="G27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I27" s="7" t="s">
+      <c r="J27" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="K27" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="K27" s="7" t="s">
+      <c r="L27" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="M27" s="7" t="s">
         <v>194</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>195</v>
       </c>
       <c r="N27" s="7"/>
       <c r="O27" s="7" t="s">
@@ -3419,40 +3414,40 @@
         <v>7017</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C28" s="5">
         <v>46235</v>
       </c>
       <c r="D28" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F28" s="5" t="s">
-        <v>172</v>
-      </c>
       <c r="G28" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J28" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="K28" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="K28" s="5" t="s">
-        <v>175</v>
-      </c>
       <c r="L28" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5" t="s">
@@ -3481,40 +3476,40 @@
         <v>7018</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C29" s="7">
         <v>46235</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E29" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>192</v>
-      </c>
       <c r="G29" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J29" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="K29" s="7" t="s">
-        <v>175</v>
-      </c>
       <c r="L29" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N29" s="7"/>
       <c r="O29" s="7" t="s">
@@ -3543,40 +3538,40 @@
         <v>7019</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C30" s="5">
         <v>46235</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>172</v>
-      </c>
       <c r="G30" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5" t="s">
@@ -3605,40 +3600,40 @@
         <v>7020</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C31" s="7">
         <v>46235</v>
       </c>
       <c r="D31" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>172</v>
-      </c>
       <c r="G31" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I31" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="M31" s="7" t="s">
         <v>200</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>201</v>
       </c>
       <c r="N31" s="7"/>
       <c r="O31" s="7" t="s">
@@ -3667,40 +3662,40 @@
         <v>7021</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C32" s="5">
         <v>46235</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I32" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I32" s="5" t="s">
+      <c r="J32" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="K32" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="J32" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>194</v>
-      </c>
       <c r="L32" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N32" s="5"/>
       <c r="O32" s="5" t="s">
@@ -3729,40 +3724,40 @@
         <v>6992</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C33" s="7">
         <v>46266</v>
       </c>
       <c r="D33" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="F33" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I33" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="I33" s="7" t="s">
+      <c r="J33" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="K33" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="K33" s="7" t="s">
+      <c r="L33" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M33" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>209</v>
       </c>
       <c r="N33" s="7"/>
       <c r="O33" s="7" t="s">
@@ -3793,40 +3788,40 @@
         <v>6993</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C34" s="5">
         <v>46266</v>
       </c>
       <c r="D34" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>205</v>
-      </c>
       <c r="F34" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I34" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="J34" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="K34" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="K34" s="5" t="s">
+      <c r="L34" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M34" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5" t="s">
@@ -3857,40 +3852,40 @@
         <v>6945</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C35" s="7">
         <v>46174</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E35" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F35" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="G35" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I35" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="J35" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="J35" s="17" t="s">
+      <c r="K35" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>219</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N35" s="8">
         <v>46219</v>
@@ -3925,53 +3920,53 @@
         <v>7036</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C36" s="5">
         <v>46266</v>
       </c>
       <c r="D36" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I36" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I36" s="5" t="s">
+      <c r="J36" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="K36" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="K36" s="5" t="s">
+      <c r="L36" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="M36" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>228</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
         <v>39</v>
       </c>
       <c r="P36" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q36" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="Q36" s="5" t="s">
+      <c r="R36" s="5" t="s">
         <v>230</v>
-      </c>
-      <c r="R36" s="5" t="s">
-        <v>231</v>
       </c>
       <c r="S36" s="5"/>
       <c r="T36" s="5" t="s">
@@ -3993,53 +3988,53 @@
         <v>7037</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C37" s="19">
         <v>46266</v>
       </c>
       <c r="D37" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="E37" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="F37" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="19" t="s">
-        <v>224</v>
-      </c>
       <c r="G37" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H37" s="19" t="s">
         <v>33</v>
       </c>
       <c r="I37" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="J37" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="K37" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="L37" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="M37" s="19" t="s">
         <v>233</v>
-      </c>
-      <c r="J37" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="K37" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="L37" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="M37" s="19" t="s">
-        <v>234</v>
       </c>
       <c r="N37" s="19"/>
       <c r="O37" s="19" t="s">
         <v>39</v>
       </c>
       <c r="P37" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q37" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="Q37" s="7" t="s">
+      <c r="R37" s="23" t="s">
         <v>230</v>
-      </c>
-      <c r="R37" s="23" t="s">
-        <v>231</v>
       </c>
       <c r="S37" s="19"/>
       <c r="T37" s="19" t="s">

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="545" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67B25243-9F31-4617-89BF-3154FF60134F}"/>
+  <xr:revisionPtr revIDLastSave="549" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AA9E0F0-B415-425F-B7DC-3023573B5740}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -680,9 +680,6 @@
     <t>ARMANDO GOMES DE ASSIS ;</t>
   </si>
   <si>
-    <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
-  </si>
-  <si>
     <t xml:space="preserve">BRASIL DISTRIBUIDORA </t>
   </si>
   <si>
@@ -699,46 +696,49 @@
     <t>CLEY MARCOS FIDELIS ;</t>
   </si>
   <si>
+    <t>VIASUPRI</t>
+  </si>
+  <si>
+    <t>Rogerio Egidio;</t>
+  </si>
+  <si>
+    <t>Yasmin Peixoto;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA JOSE BONIFACIO, Num.: 1853 Comple.: , Bairro: SERRARIA / </t>
+  </si>
+  <si>
+    <t>financeiro@viasupri.com.br;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 91481-5736 / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CARNEIRO BENICIO ; </t>
+  </si>
+  <si>
+    <t>Aline</t>
+  </si>
+  <si>
+    <t>financeiro@viasupri.com.br</t>
+  </si>
+  <si>
+    <t>(11) 9181-5736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE BONIFACIO, Num.: 1853 Comple.: ANDAR 01, Bairro: SERRARIA / </t>
+  </si>
+  <si>
+    <t>MARIA SOCORRO BENÍCIO DA SILVA ;</t>
+  </si>
+  <si>
+    <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+  </si>
+  <si>
     <t>VIASUPRI SUPRIMENTOS DE ESCRITORIO E LIMPEZA LTDA</t>
   </si>
   <si>
-    <t>VIASUPRI</t>
-  </si>
-  <si>
-    <t>Rogerio Egidio;</t>
-  </si>
-  <si>
-    <t>Yasmin Peixoto;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUA JOSE BONIFACIO, Num.: 1853 Comple.: , Bairro: SERRARIA / </t>
-  </si>
-  <si>
-    <t>financeiro@viasupri.com.br;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11) 91481-5736 / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIA CARNEIRO BENICIO ; </t>
-  </si>
-  <si>
-    <t>Aline</t>
-  </si>
-  <si>
-    <t>financeiro@viasupri.com.br</t>
-  </si>
-  <si>
-    <t>(11) 9181-5736</t>
-  </si>
-  <si>
     <t>EXPAND COMERCIO E SERVICOS ADMINISTRATIVOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOSE BONIFACIO, Num.: 1853 Comple.: ANDAR 01, Bairro: SERRARIA / </t>
-  </si>
-  <si>
-    <t>MARIA SOCORRO BENÍCIO DA SILVA ;</t>
   </si>
 </sst>
 </file>
@@ -932,8 +932,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -945,6 +943,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1602,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AB41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -1717,7 +1717,7 @@
       <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="20" t="s">
+      <c r="AB1" s="18" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
-      <c r="AB2" s="21"/>
+      <c r="AB2" s="19"/>
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="6">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
-      <c r="AB3" s="22"/>
+      <c r="AB3" s="20"/>
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="4">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="Z11" s="7"/>
       <c r="AA11" s="7"/>
-      <c r="AB11" s="22"/>
+      <c r="AB11" s="20"/>
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="4">
@@ -3139,7 +3139,7 @@
       <c r="M23" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="N23" s="12"/>
+      <c r="N23" s="21"/>
       <c r="O23" s="7" t="s">
         <v>39</v>
       </c>
@@ -3201,7 +3201,7 @@
       <c r="M24" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="N24" s="13"/>
+      <c r="N24" s="22"/>
       <c r="O24" s="5" t="s">
         <v>39</v>
       </c>
@@ -3325,7 +3325,7 @@
       <c r="M26" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="N26" s="13"/>
+      <c r="N26" s="22"/>
       <c r="O26" s="5" t="s">
         <v>39</v>
       </c>
@@ -3784,7 +3784,7 @@
       <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:28">
-      <c r="A34" s="14">
+      <c r="A34" s="12">
         <v>6993</v>
       </c>
       <c r="B34" s="5" t="s">
@@ -3848,17 +3848,14 @@
       <c r="AB34" s="5"/>
     </row>
     <row r="35" spans="1:28" ht="17.25" customHeight="1">
-      <c r="A35" s="15">
+      <c r="A35" s="13">
         <v>6945</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>214</v>
       </c>
       <c r="C35" s="7">
         <v>46174</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>148</v>
@@ -3872,20 +3869,20 @@
       <c r="H35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I35" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="J35" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="J35" s="17" t="s">
+      <c r="K35" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N35" s="8">
         <v>46219</v>
@@ -3916,23 +3913,20 @@
       <c r="AB35" s="7"/>
     </row>
     <row r="36" spans="1:28">
-      <c r="A36" s="14">
+      <c r="A36" s="12">
         <v>7036</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="C36" s="5">
         <v>46266</v>
       </c>
       <c r="D36" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>223</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>150</v>
@@ -3941,32 +3935,32 @@
         <v>102</v>
       </c>
       <c r="I36" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="K36" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>64</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
         <v>39</v>
       </c>
       <c r="P36" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="R36" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="Q36" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="R36" s="5" t="s">
-        <v>230</v>
       </c>
       <c r="S36" s="5"/>
       <c r="T36" s="5" t="s">
@@ -3984,72 +3978,84 @@
       <c r="AB36" s="5"/>
     </row>
     <row r="37" spans="1:28">
-      <c r="A37" s="18">
+      <c r="A37" s="16">
         <v>7037</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="C37" s="17">
+        <v>46266</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="L37" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="M37" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="R37" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z37" s="17"/>
+      <c r="AA37" s="17"/>
+      <c r="AB37" s="17"/>
+    </row>
+    <row r="39" spans="1:28">
+      <c r="B39" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="C37" s="19">
-        <v>46266</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="H37" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="I37" s="19" t="s">
+    </row>
+    <row r="40" spans="1:28">
+      <c r="B40" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="J37" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="K37" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="L37" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="M37" s="19" t="s">
+    </row>
+    <row r="41" spans="1:28">
+      <c r="B41" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="P37" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q37" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="R37" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="S37" s="19"/>
-      <c r="T37" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="U37" s="19"/>
-      <c r="V37" s="19"/>
-      <c r="W37" s="19"/>
-      <c r="X37" s="19"/>
-      <c r="Y37" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z37" s="19"/>
-      <c r="AA37" s="19"/>
-      <c r="AB37" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="549" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AA9E0F0-B415-425F-B7DC-3023573B5740}"/>
+  <xr:revisionPtr revIDLastSave="550" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{523D76C6-5981-4B57-9977-08696B38E977}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -680,6 +680,9 @@
     <t>ARMANDO GOMES DE ASSIS ;</t>
   </si>
   <si>
+    <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRASIL DISTRIBUIDORA </t>
   </si>
   <si>
@@ -696,6 +699,9 @@
     <t>CLEY MARCOS FIDELIS ;</t>
   </si>
   <si>
+    <t>VIASUPRI SUPRIMENTOS DE ESCRITORIO E LIMPEZA LTDA</t>
+  </si>
+  <si>
     <t>VIASUPRI</t>
   </si>
   <si>
@@ -726,19 +732,13 @@
     <t>(11) 9181-5736</t>
   </si>
   <si>
+    <t>EXPAND COMERCIO E SERVICOS ADMINISTRATIVOS LTDA</t>
+  </si>
+  <si>
     <t xml:space="preserve">JOSE BONIFACIO, Num.: 1853 Comple.: ANDAR 01, Bairro: SERRARIA / </t>
   </si>
   <si>
     <t>MARIA SOCORRO BENÍCIO DA SILVA ;</t>
-  </si>
-  <si>
-    <t>BRASIL DISTRIBUIDORA DE PEÇAS LTDA</t>
-  </si>
-  <si>
-    <t>VIASUPRI SUPRIMENTOS DE ESCRITORIO E LIMPEZA LTDA</t>
-  </si>
-  <si>
-    <t>EXPAND COMERCIO E SERVICOS ADMINISTRATIVOS LTDA</t>
   </si>
 </sst>
 </file>
@@ -1602,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB41"/>
+  <dimension ref="A1:AB37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -3851,11 +3851,14 @@
       <c r="A35" s="13">
         <v>6945</v>
       </c>
+      <c r="B35" s="7" t="s">
+        <v>214</v>
+      </c>
       <c r="C35" s="7">
         <v>46174</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>148</v>
@@ -3870,19 +3873,19 @@
         <v>33</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N35" s="8">
         <v>46219</v>
@@ -3916,17 +3919,20 @@
       <c r="A36" s="12">
         <v>7036</v>
       </c>
+      <c r="B36" s="5" t="s">
+        <v>220</v>
+      </c>
       <c r="C36" s="5">
         <v>46266</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>150</v>
@@ -3935,32 +3941,32 @@
         <v>102</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>64</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
         <v>39</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q36" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="R36" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="S36" s="5"/>
       <c r="T36" s="5" t="s">
@@ -3981,17 +3987,20 @@
       <c r="A37" s="16">
         <v>7037</v>
       </c>
+      <c r="B37" s="17" t="s">
+        <v>231</v>
+      </c>
       <c r="C37" s="17">
         <v>46266</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G37" s="17" t="s">
         <v>150</v>
@@ -4000,32 +4009,32 @@
         <v>33</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K37" s="17" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L37" s="17" t="s">
         <v>64</v>
       </c>
       <c r="M37" s="17" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N37" s="17"/>
       <c r="O37" s="17" t="s">
         <v>39</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="R37" s="23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="S37" s="17"/>
       <c r="T37" s="17" t="s">
@@ -4041,21 +4050,6 @@
       <c r="Z37" s="17"/>
       <c r="AA37" s="17"/>
       <c r="AB37" s="17"/>
-    </row>
-    <row r="39" spans="1:28">
-      <c r="B39" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28">
-      <c r="B40" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28">
-      <c r="B41" s="17" t="s">
-        <v>233</v>
-      </c>
     </row>
   </sheetData>
   <dataValidations count="5">

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="550" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{523D76C6-5981-4B57-9977-08696B38E977}"/>
+  <xr:revisionPtr revIDLastSave="552" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D01FEDD0-6EC9-4932-97FC-DC73977719B1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="552" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D01FEDD0-6EC9-4932-97FC-DC73977719B1}"/>
+  <xr:revisionPtr revIDLastSave="582" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B302B61B-F6AF-4175-8BE1-1778158AB9FF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="235">
   <si>
     <t>ID</t>
   </si>
@@ -564,6 +564,9 @@
   </si>
   <si>
     <t>AA&amp;amp;MARTINS PARTICIPACOES LTDA ;ADRIANO AUGUSTO MARTINS ;E&amp;amp;G MARTINS PARTICIPACOES LTDA ;EDUARDO DE JESUS MARTINS  ; B&amp;amp;SOLAR PARTICIPACOES LTDA ;MARCOS MARQUES MARTINS ;</t>
+  </si>
+  <si>
+    <t>Karina Santos</t>
   </si>
   <si>
     <t>COMERCIO VAREJISTA DE MERCADORIAS 3M LTDA (FILIAL 1)</t>
@@ -919,7 +922,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -929,7 +932,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -937,15 +939,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1717,7 +1717,7 @@
       <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="18" t="s">
+      <c r="AB1" s="16" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
-      <c r="AB2" s="19"/>
+      <c r="AB2" s="17"/>
     </row>
     <row r="3" spans="1:28">
       <c r="A3" s="6">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
-      <c r="AB3" s="20"/>
+      <c r="AB3" s="18"/>
     </row>
     <row r="4" spans="1:28">
       <c r="A4" s="4">
@@ -1877,7 +1877,7 @@
       <c r="I4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="5" t="s">
         <v>52</v>
       </c>
       <c r="K4" s="5" t="s">
@@ -1889,7 +1889,7 @@
       <c r="M4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9">
         <v>46232</v>
       </c>
       <c r="O4" s="5" t="s">
@@ -1898,7 +1898,7 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
-      <c r="S4" s="10">
+      <c r="S4" s="9">
         <v>46232</v>
       </c>
       <c r="T4" s="5" t="s">
@@ -1907,7 +1907,7 @@
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
-      <c r="X4" s="10">
+      <c r="X4" s="9">
         <v>46253</v>
       </c>
       <c r="Y4" s="5" t="s">
@@ -2019,7 +2019,7 @@
       <c r="M6" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="9">
         <v>46245</v>
       </c>
       <c r="O6" s="5" t="s">
@@ -2028,7 +2028,7 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
-      <c r="S6" s="10">
+      <c r="S6" s="9">
         <v>46245</v>
       </c>
       <c r="T6" s="5" t="s">
@@ -2037,7 +2037,7 @@
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
-      <c r="X6" s="10">
+      <c r="X6" s="9">
         <v>46246</v>
       </c>
       <c r="Y6" s="5" t="s">
@@ -2169,7 +2169,7 @@
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
-      <c r="X8" s="10">
+      <c r="X8" s="9">
         <v>46253</v>
       </c>
       <c r="Y8" s="5" t="s">
@@ -2287,7 +2287,7 @@
       <c r="M10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="9">
         <v>46255</v>
       </c>
       <c r="O10" s="5" t="s">
@@ -2296,7 +2296,7 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="10">
+      <c r="S10" s="9">
         <v>46255</v>
       </c>
       <c r="T10" s="5" t="s">
@@ -2305,7 +2305,7 @@
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
       <c r="W10" s="5"/>
-      <c r="X10" s="10">
+      <c r="X10" s="9">
         <v>46191</v>
       </c>
       <c r="Y10" s="5" t="s">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="Z11" s="7"/>
       <c r="AA11" s="7"/>
-      <c r="AB11" s="20"/>
+      <c r="AB11" s="18"/>
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="4">
@@ -2417,7 +2417,7 @@
       <c r="M12" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="9">
         <v>46252</v>
       </c>
       <c r="O12" s="5" t="s">
@@ -2426,7 +2426,7 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
-      <c r="S12" s="10">
+      <c r="S12" s="9">
         <v>46252</v>
       </c>
       <c r="T12" s="5" t="s">
@@ -2435,7 +2435,7 @@
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
       <c r="W12" s="5"/>
-      <c r="X12" s="10">
+      <c r="X12" s="9">
         <v>46245</v>
       </c>
       <c r="Y12" s="5" t="s">
@@ -2455,7 +2455,7 @@
       <c r="C13" s="7">
         <v>46266</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="10" t="s">
         <v>108</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -2497,12 +2497,12 @@
       <c r="S13" s="8">
         <v>46259</v>
       </c>
-      <c r="T13" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
+      <c r="T13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
       <c r="X13" s="8">
         <v>46245</v>
       </c>
@@ -2553,7 +2553,7 @@
       <c r="M14" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="9">
         <v>46232</v>
       </c>
       <c r="O14" s="5" t="s">
@@ -2562,7 +2562,7 @@
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
-      <c r="S14" s="10">
+      <c r="S14" s="9">
         <v>46232</v>
       </c>
       <c r="T14" s="5" t="s">
@@ -2685,7 +2685,7 @@
       <c r="M16" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="9">
         <v>46253</v>
       </c>
       <c r="O16" s="5" t="s">
@@ -2694,7 +2694,7 @@
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
-      <c r="S16" s="10">
+      <c r="S16" s="9">
         <v>46233</v>
       </c>
       <c r="T16" s="5" t="s">
@@ -2703,7 +2703,7 @@
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
       <c r="W16" s="5"/>
-      <c r="X16" s="10">
+      <c r="X16" s="9">
         <v>46251</v>
       </c>
       <c r="Y16" s="5" t="s">
@@ -2819,7 +2819,7 @@
       <c r="M18" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="9">
         <v>46205</v>
       </c>
       <c r="O18" s="5" t="s">
@@ -2828,7 +2828,7 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
-      <c r="S18" s="10">
+      <c r="S18" s="9">
         <v>46205</v>
       </c>
       <c r="T18" s="5" t="s">
@@ -2837,7 +2837,7 @@
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
       <c r="W18" s="5"/>
-      <c r="X18" s="10">
+      <c r="X18" s="9">
         <v>46216</v>
       </c>
       <c r="Y18" s="5" t="s">
@@ -3139,11 +3139,15 @@
       <c r="M23" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="N23" s="21"/>
+      <c r="N23" s="20">
+        <v>46255</v>
+      </c>
       <c r="O23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P23" s="7"/>
+      <c r="P23" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
@@ -3166,7 +3170,7 @@
         <v>7012</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C24" s="5">
         <v>46235</v>
@@ -3187,7 +3191,7 @@
         <v>102</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>173</v>
@@ -3199,13 +3203,17 @@
         <v>64</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="N24" s="22"/>
+        <v>179</v>
+      </c>
+      <c r="N24" s="20">
+        <v>46255</v>
+      </c>
       <c r="O24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P24" s="5"/>
+      <c r="P24" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
@@ -3228,7 +3236,7 @@
         <v>7014</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C25" s="7">
         <v>46235</v>
@@ -3249,25 +3257,29 @@
         <v>93</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="N25" s="7"/>
+        <v>185</v>
+      </c>
+      <c r="N25" s="20">
+        <v>46255</v>
+      </c>
       <c r="O25" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P25" s="7"/>
+      <c r="P25" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
@@ -3290,7 +3302,7 @@
         <v>7015</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C26" s="5">
         <v>46235</v>
@@ -3311,10 +3323,10 @@
         <v>93</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>174</v>
@@ -3323,13 +3335,17 @@
         <v>64</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="N26" s="22"/>
+        <v>189</v>
+      </c>
+      <c r="N26" s="20">
+        <v>46255</v>
+      </c>
       <c r="O26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P26" s="5"/>
+      <c r="P26" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
@@ -3352,7 +3368,7 @@
         <v>7016</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C27" s="7">
         <v>46235</v>
@@ -3361,10 +3377,10 @@
         <v>169</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>150</v>
@@ -3373,25 +3389,29 @@
         <v>93</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="N27" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="N27" s="20">
+        <v>46255</v>
+      </c>
       <c r="O27" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P27" s="7"/>
+      <c r="P27" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
@@ -3414,7 +3434,7 @@
         <v>7017</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C28" s="5">
         <v>46235</v>
@@ -3435,7 +3455,7 @@
         <v>93</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>173</v>
@@ -3447,13 +3467,17 @@
         <v>64</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="N28" s="5"/>
+        <v>195</v>
+      </c>
+      <c r="N28" s="20">
+        <v>46255</v>
+      </c>
       <c r="O28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P28" s="5"/>
+      <c r="P28" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
@@ -3476,7 +3500,7 @@
         <v>7018</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C29" s="7">
         <v>46235</v>
@@ -3485,10 +3509,10 @@
         <v>169</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>150</v>
@@ -3497,7 +3521,7 @@
         <v>93</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>173</v>
@@ -3509,13 +3533,17 @@
         <v>64</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="N29" s="7"/>
+        <v>185</v>
+      </c>
+      <c r="N29" s="20">
+        <v>46255</v>
+      </c>
       <c r="O29" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P29" s="7"/>
+      <c r="P29" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
@@ -3538,7 +3566,7 @@
         <v>7019</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C30" s="5">
         <v>46235</v>
@@ -3559,10 +3587,10 @@
         <v>93</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>174</v>
@@ -3571,13 +3599,17 @@
         <v>64</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="N30" s="5"/>
+        <v>185</v>
+      </c>
+      <c r="N30" s="20">
+        <v>46255</v>
+      </c>
       <c r="O30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P30" s="5"/>
+      <c r="P30" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -3600,7 +3632,7 @@
         <v>7020</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="7">
         <v>46235</v>
@@ -3621,25 +3653,29 @@
         <v>93</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="N31" s="7"/>
+        <v>201</v>
+      </c>
+      <c r="N31" s="20">
+        <v>46255</v>
+      </c>
       <c r="O31" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P31" s="7"/>
+      <c r="P31" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
       <c r="S31" s="7"/>
@@ -3662,7 +3698,7 @@
         <v>7021</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C32" s="5">
         <v>46235</v>
@@ -3671,10 +3707,10 @@
         <v>169</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>150</v>
@@ -3683,25 +3719,29 @@
         <v>93</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="N32" s="5"/>
+        <v>201</v>
+      </c>
+      <c r="N32" s="20">
+        <v>46255</v>
+      </c>
       <c r="O32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P32" s="5"/>
+      <c r="P32" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5"/>
@@ -3724,16 +3764,16 @@
         <v>6992</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C33" s="7">
         <v>46266</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>149</v>
@@ -3745,19 +3785,19 @@
         <v>102</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N33" s="7"/>
       <c r="O33" s="7" t="s">
@@ -3784,20 +3824,20 @@
       <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:28">
-      <c r="A34" s="12">
+      <c r="A34" s="11">
         <v>6993</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C34" s="5">
         <v>46266</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>149</v>
@@ -3809,19 +3849,19 @@
         <v>33</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>64</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5" t="s">
@@ -3837,7 +3877,7 @@
       <c r="U34" s="5"/>
       <c r="V34" s="5"/>
       <c r="W34" s="5"/>
-      <c r="X34" s="10">
+      <c r="X34" s="9">
         <v>46247</v>
       </c>
       <c r="Y34" s="5" t="s">
@@ -3848,17 +3888,17 @@
       <c r="AB34" s="5"/>
     </row>
     <row r="35" spans="1:28" ht="17.25" customHeight="1">
-      <c r="A35" s="13">
+      <c r="A35" s="12">
         <v>6945</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C35" s="7">
         <v>46174</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>148</v>
@@ -3872,20 +3912,20 @@
       <c r="H35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I35" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="J35" s="15" t="s">
+      <c r="I35" s="13" t="s">
         <v>217</v>
       </c>
+      <c r="J35" s="7" t="s">
+        <v>218</v>
+      </c>
       <c r="K35" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N35" s="8">
         <v>46219</v>
@@ -3916,23 +3956,23 @@
       <c r="AB35" s="7"/>
     </row>
     <row r="36" spans="1:28">
-      <c r="A36" s="12">
+      <c r="A36" s="11">
         <v>7036</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C36" s="5">
         <v>46266</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>150</v>
@@ -3941,32 +3981,32 @@
         <v>102</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>64</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
         <v>39</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q36" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="R36" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="S36" s="5"/>
       <c r="T36" s="5" t="s">
@@ -3984,72 +4024,72 @@
       <c r="AB36" s="5"/>
     </row>
     <row r="37" spans="1:28">
-      <c r="A37" s="16">
+      <c r="A37" s="14">
         <v>7037</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="C37" s="15">
+        <v>46266</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="R37" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="C37" s="17">
-        <v>46266</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="I37" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="J37" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="K37" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="L37" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="M37" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="P37" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q37" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="R37" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="S37" s="17"/>
-      <c r="T37" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="U37" s="17"/>
-      <c r="V37" s="17"/>
-      <c r="W37" s="17"/>
-      <c r="X37" s="17"/>
-      <c r="Y37" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z37" s="17"/>
-      <c r="AA37" s="17"/>
-      <c r="AB37" s="17"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
+      <c r="Y37" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z37" s="15"/>
+      <c r="AA37" s="15"/>
+      <c r="AB37" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="5">
